--- a/backend/storage/schema/quotation_template.xlsx
+++ b/backend/storage/schema/quotation_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/longlh123/Languages/GitHub/IPSOS-FINANCE-PAYMENT/backend/storage/schema/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F9C721-C881-DE40-B953-21728DC345A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3133C9E8-F336-7E4F-86B8-05399630F615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6260" yWindow="3100" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{C9138D76-07EC-41C4-8817-AFCBF30C50C2}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="195">
   <si>
     <t>field_name</t>
   </si>
@@ -103,10 +103,7 @@
     <t>Loại hình dự án</t>
   </si>
   <si>
-    <t>Quy cách đặt mẫu (Dự án HUT)</t>
-  </si>
-  <si>
-    <t>Tablet/Laptop</t>
+    <t>Phương pháp sampling</t>
   </si>
   <si>
     <t>hut_sample_specification</t>
@@ -127,30 +124,6 @@
     <t>open_question_count</t>
   </si>
   <si>
-    <t>Có danh sách từ KH không</t>
-  </si>
-  <si>
-    <t>Yêu cầu ghi âm</t>
-  </si>
-  <si>
-    <t>Yêu cầu chụp hình</t>
-  </si>
-  <si>
-    <t>Tài liệu yêu cầu thu thập</t>
-  </si>
-  <si>
-    <t>client_provided_list</t>
-  </si>
-  <si>
-    <t>audio_recording_required</t>
-  </si>
-  <si>
-    <t>photo_required</t>
-  </si>
-  <si>
-    <t>required_documents</t>
-  </si>
-  <si>
     <t>number</t>
   </si>
   <si>
@@ -208,9 +181,6 @@
     <t>sampling_methods</t>
   </si>
   <si>
-    <t>Sample Method</t>
-  </si>
-  <si>
     <t>Random sampling</t>
   </si>
   <si>
@@ -220,6 +190,9 @@
     <t>Other</t>
   </si>
   <si>
+    <t>range</t>
+  </si>
+  <si>
     <t>default_value</t>
   </si>
   <si>
@@ -259,9 +232,6 @@
     <t>target_audiences</t>
   </si>
   <si>
-    <t>repeater_card</t>
-  </si>
-  <si>
     <t>target_audiences_config</t>
   </si>
   <si>
@@ -274,15 +244,6 @@
     <t>excel:platform</t>
   </si>
   <si>
-    <t>excel:hut_sample_specification</t>
-  </si>
-  <si>
-    <t>excel:device_requirement</t>
-  </si>
-  <si>
-    <t>excel:yes_no_question</t>
-  </si>
-  <si>
     <t>db:project_types</t>
   </si>
   <si>
@@ -310,18 +271,12 @@
     <t>project_types</t>
   </si>
   <si>
-    <t>interview_method_config</t>
-  </si>
-  <si>
     <t>interview_methods</t>
   </si>
   <si>
     <t>excel:sampling_methods</t>
   </si>
   <si>
-    <t>Phương pháp phỏng vấn &amp; Phương pháp sampling</t>
-  </si>
-  <si>
     <t>sampling_questionnaire_design</t>
   </si>
   <si>
@@ -334,26 +289,357 @@
     <t>sample_types</t>
   </si>
   <si>
-    <t>Interview Method</t>
-  </si>
-  <si>
     <t>excel:sample_types</t>
   </si>
   <si>
-    <t>Interview Length (min)</t>
-  </si>
-  <si>
-    <t>Number of Open-Ended questions</t>
+    <t>section</t>
+  </si>
+  <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>Giới Tính</t>
+  </si>
+  <si>
+    <t>excel:gender</t>
+  </si>
+  <si>
+    <t>Nam</t>
+  </si>
+  <si>
+    <t>Nữ</t>
+  </si>
+  <si>
+    <t>Nam/Nữ</t>
+  </si>
+  <si>
+    <t>age_group</t>
+  </si>
+  <si>
+    <t>Độ tuổi</t>
+  </si>
+  <si>
+    <t>household_incomes</t>
+  </si>
+  <si>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>excel:household_incomes</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>respondent_conditions</t>
+  </si>
+  <si>
+    <t>Điều kiện đáp viên</t>
+  </si>
+  <si>
+    <t>bumo</t>
+  </si>
+  <si>
+    <t>BUMO</t>
+  </si>
+  <si>
+    <t>Độ dài phỏng vấn (phút)</t>
+  </si>
+  <si>
+    <t>Số lượng câu hỏi mở</t>
+  </si>
+  <si>
+    <t>Phương pháp phỏng vấn</t>
+  </si>
+  <si>
+    <t>booster_conditions</t>
+  </si>
+  <si>
+    <t>Điều kiện tuyển Booster</t>
+  </si>
+  <si>
+    <t>provinces</t>
+  </si>
+  <si>
+    <t>Khu vực thực hiện</t>
+  </si>
+  <si>
+    <t>implementation_area</t>
+  </si>
+  <si>
+    <t>implementation_area_config</t>
+  </si>
+  <si>
+    <t>db:provinces</t>
+  </si>
+  <si>
+    <t>sample_size</t>
+  </si>
+  <si>
+    <t>Sample Size</t>
+  </si>
+  <si>
+    <t>Province</t>
+  </si>
+  <si>
+    <t>quota_control</t>
+  </si>
+  <si>
+    <t>Quota</t>
+  </si>
+  <si>
+    <t>quota_control_config</t>
+  </si>
+  <si>
+    <t>Type of Quota Control</t>
+  </si>
+  <si>
+    <t>excel:quota_control_types</t>
+  </si>
+  <si>
+    <t>quota_control_types</t>
+  </si>
+  <si>
+    <t>No Quota</t>
+  </si>
+  <si>
+    <t>Parallel Flexiable Quota</t>
+  </si>
+  <si>
+    <t>Parallel Fixed Quota</t>
+  </si>
+  <si>
+    <t>Interlocked Quota</t>
+  </si>
+  <si>
+    <t>Quota Description</t>
+  </si>
+  <si>
+    <t>excel:quota_descriptions</t>
+  </si>
+  <si>
+    <t>quota_descriptions</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Age Group</t>
+  </si>
+  <si>
+    <t>quality_control_requirements</t>
+  </si>
+  <si>
+    <t>Yêu cầu về QC</t>
+  </si>
+  <si>
+    <t>quality_control_requirements_config</t>
+  </si>
+  <si>
+    <t>Sampling</t>
+  </si>
+  <si>
+    <t>type_of_quota_controls</t>
+  </si>
+  <si>
+    <t>quota_description</t>
+  </si>
+  <si>
+    <t>qc_ratio</t>
+  </si>
+  <si>
+    <t>Tỉ lệ QC (% số bài / PVV)</t>
+  </si>
+  <si>
+    <t>Check OE</t>
+  </si>
+  <si>
+    <t>Yêu cầu khác về QC</t>
+  </si>
+  <si>
+    <t>qc_sampling</t>
+  </si>
+  <si>
+    <t>qc_open_ended</t>
+  </si>
+  <si>
+    <t>qc_other</t>
+  </si>
+  <si>
+    <t>data_processing_requirements</t>
+  </si>
+  <si>
+    <t>Yêu cầu về DP</t>
+  </si>
+  <si>
+    <t>data_processing_requirements_config</t>
+  </si>
+  <si>
+    <t>dp_scripting</t>
+  </si>
+  <si>
+    <t>dp_codeframe</t>
+  </si>
+  <si>
+    <t>DP VN viết link</t>
+  </si>
+  <si>
+    <t>DP VN làm codeframe</t>
+  </si>
+  <si>
+    <t>DP VN chạy data</t>
+  </si>
+  <si>
+    <t>dp_other</t>
+  </si>
+  <si>
+    <t>Yêu cầu khác về DP</t>
+  </si>
+  <si>
+    <t>excel:data_processing</t>
+  </si>
+  <si>
+    <t>data_processing</t>
+  </si>
+  <si>
+    <t>Tabspec</t>
+  </si>
+  <si>
+    <t>Topline</t>
+  </si>
+  <si>
+    <t>SPSS</t>
+  </si>
+  <si>
+    <t>OE</t>
+  </si>
+  <si>
+    <t>dp_data_processing</t>
+  </si>
+  <si>
+    <t>Phương Pháp</t>
+  </si>
+  <si>
+    <t>fieldwork_design</t>
+  </si>
+  <si>
+    <t>fieldwork_design_config</t>
+  </si>
+  <si>
+    <t>Loại hình nghiên cứu</t>
+  </si>
+  <si>
+    <t>research_type</t>
+  </si>
+  <si>
+    <t>excel:research_type</t>
+  </si>
+  <si>
+    <t>product_type</t>
+  </si>
+  <si>
+    <t>Sản phẩm nghiên cứu</t>
+  </si>
+  <si>
+    <t>Nước giặt</t>
+  </si>
+  <si>
+    <t>Bột giặt</t>
+  </si>
+  <si>
+    <t>Nước rửa chén</t>
+  </si>
+  <si>
+    <t>Nước xả vải</t>
+  </si>
+  <si>
+    <t>Thuốc lá</t>
+  </si>
+  <si>
+    <t>Bia</t>
+  </si>
+  <si>
+    <t>excel:product_type</t>
+  </si>
+  <si>
+    <t>Product Test - Monadic</t>
+  </si>
+  <si>
+    <t>Concept Test - Monadic</t>
+  </si>
+  <si>
+    <t>Product Test - Sequential Monadic</t>
+  </si>
+  <si>
+    <t>Concept Test - Sequential Monadic</t>
+  </si>
+  <si>
+    <t>number_of_test_products</t>
+  </si>
+  <si>
+    <t>products_per_respondent</t>
+  </si>
+  <si>
+    <t>Số lượng sản phẩm test trên mỗi đáp viên</t>
+  </si>
+  <si>
+    <t>Tổng số sản phẩm test</t>
+  </si>
+  <si>
+    <t>number_of_test_concepts</t>
+  </si>
+  <si>
+    <t>concepts_per_respondent</t>
+  </si>
+  <si>
+    <t>Tổng số concept test</t>
+  </si>
+  <si>
+    <t>Số lượng concept test trên mỗi đáp viên</t>
+  </si>
+  <si>
+    <t>field_work_design_comment</t>
+  </si>
+  <si>
+    <t>Ghi chú thêm</t>
+  </si>
+  <si>
+    <t>usage_duration</t>
+  </si>
+  <si>
+    <t>Số ngày sử dụng mỗi sản phẩm</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -379,11 +665,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -718,7 +1005,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6694FA44-4A7D-4629-A892-7DFDEEB80386}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -744,27 +1031,27 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -890,19 +1177,19 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="B8" t="s">
         <v>20</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="H8">
         <v>12</v>
@@ -916,7 +1203,7 @@
         <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -927,19 +1214,19 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H10">
         <v>12</v>
@@ -947,19 +1234,19 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>91</v>
+        <v>165</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
-      </c>
-      <c r="C11" t="s">
-        <v>38</v>
+        <v>164</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
-      <c r="F11" t="s">
-        <v>90</v>
+      <c r="F11" s="2" t="s">
+        <v>166</v>
       </c>
       <c r="H11">
         <v>12</v>
@@ -967,19 +1254,19 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="H12">
         <v>12</v>
@@ -987,19 +1274,19 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="H13">
         <v>12</v>
@@ -1007,19 +1294,19 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
-      <c r="G14" t="s">
-        <v>78</v>
+      <c r="F14" t="s">
+        <v>114</v>
       </c>
       <c r="H14">
         <v>12</v>
@@ -1027,19 +1314,19 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
-      <c r="G15" t="s">
-        <v>79</v>
+      <c r="F15" t="s">
+        <v>121</v>
       </c>
       <c r="H15">
         <v>12</v>
@@ -1047,77 +1334,46 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>135</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
-      <c r="G16" t="s">
-        <v>80</v>
-      </c>
-      <c r="H16">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F16" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>147</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>148</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
-      <c r="G17" t="s">
-        <v>80</v>
-      </c>
-      <c r="H17">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>12</v>
-      </c>
+      <c r="F17" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C19" s="1"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C20" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1127,7 +1383,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2B8FC54-75D4-4AC2-B92C-338AB72929A6}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.83203125" bestFit="1" customWidth="1"/>
@@ -1140,7 +1396,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1155,103 +1411,605 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>90</v>
+      <c r="A2" s="2" t="s">
+        <v>166</v>
       </c>
       <c r="B2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C8" t="s">
+        <v>190</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B9" t="s">
+        <v>193</v>
+      </c>
+      <c r="C9" t="s">
+        <v>194</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B11" t="s">
+        <v>191</v>
+      </c>
+      <c r="C11" t="s">
+        <v>192</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="G15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" t="s">
         <v>91</v>
       </c>
-      <c r="C2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="C16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="G21" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" t="s">
         <v>7</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="G4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="G22" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>114</v>
+      </c>
+      <c r="B23" t="s">
+        <v>116</v>
+      </c>
+      <c r="C23" t="s">
+        <v>117</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6">
+      <c r="E23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>121</v>
+      </c>
+      <c r="B24" t="s">
+        <v>138</v>
+      </c>
+      <c r="C24" t="s">
+        <v>122</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="G24" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>121</v>
+      </c>
+      <c r="B25" t="s">
+        <v>139</v>
+      </c>
+      <c r="C25" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="G25" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>136</v>
+      </c>
+      <c r="B26" t="s">
+        <v>144</v>
+      </c>
+      <c r="C26" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B27" t="s">
+        <v>140</v>
+      </c>
+      <c r="C27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>136</v>
+      </c>
+      <c r="B28" t="s">
+        <v>145</v>
+      </c>
+      <c r="C28" t="s">
+        <v>142</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>136</v>
+      </c>
+      <c r="B29" t="s">
+        <v>146</v>
+      </c>
+      <c r="C29" t="s">
+        <v>143</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>149</v>
+      </c>
+      <c r="B30" t="s">
+        <v>150</v>
+      </c>
+      <c r="C30" t="s">
+        <v>152</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="G30" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>149</v>
+      </c>
+      <c r="B31" t="s">
+        <v>151</v>
+      </c>
+      <c r="C31" t="s">
+        <v>153</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="G31" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>149</v>
+      </c>
+      <c r="B32" t="s">
+        <v>163</v>
+      </c>
+      <c r="C32" t="s">
+        <v>154</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="G32" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>149</v>
+      </c>
+      <c r="B33" t="s">
+        <v>155</v>
+      </c>
+      <c r="C33" t="s">
+        <v>156</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E33">
         <v>1</v>
       </c>
     </row>
@@ -1262,20 +2020,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{256469AD-8C25-494B-B7FC-7D7B2DDE1DC0}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -1283,189 +2041,530 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3">
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+      <c r="C20" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24">
+        <v>3</v>
+      </c>
+      <c r="C24" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25">
+        <v>4</v>
+      </c>
+      <c r="C25" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26">
+        <v>5</v>
+      </c>
+      <c r="C26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27">
+        <v>6</v>
+      </c>
+      <c r="C27" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29">
+        <v>2</v>
+      </c>
+      <c r="C29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>124</v>
+      </c>
+      <c r="B30">
+        <v>3</v>
+      </c>
+      <c r="C30" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>124</v>
+      </c>
+      <c r="B31">
+        <v>4</v>
+      </c>
+      <c r="C31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>131</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>131</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>131</v>
+      </c>
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>131</v>
+      </c>
+      <c r="B35">
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>158</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>158</v>
+      </c>
+      <c r="B37">
+        <v>2</v>
+      </c>
+      <c r="C37" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>158</v>
+      </c>
+      <c r="B38">
+        <v>3</v>
+      </c>
+      <c r="C38" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>158</v>
+      </c>
+      <c r="B39">
+        <v>4</v>
+      </c>
+      <c r="C39" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>168</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>168</v>
+      </c>
+      <c r="B41">
+        <v>2</v>
+      </c>
+      <c r="C41" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>168</v>
+      </c>
+      <c r="B42">
+        <v>3</v>
+      </c>
+      <c r="C42" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>168</v>
+      </c>
+      <c r="B43">
+        <v>4</v>
+      </c>
+      <c r="C43" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>170</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>170</v>
+      </c>
+      <c r="B45">
+        <v>2</v>
+      </c>
+      <c r="C45" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>170</v>
+      </c>
+      <c r="B46">
+        <v>3</v>
+      </c>
+      <c r="C46" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>170</v>
+      </c>
+      <c r="B47">
+        <v>4</v>
+      </c>
+      <c r="C47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>170</v>
+      </c>
+      <c r="B48">
+        <v>5</v>
+      </c>
+      <c r="C48" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>170</v>
+      </c>
+      <c r="B49">
+        <v>6</v>
+      </c>
+      <c r="C49" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/backend/storage/schema/quotation_template.xlsx
+++ b/backend/storage/schema/quotation_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/longlh123/Languages/GitHub/IPSOS-FINANCE-PAYMENT/backend/storage/schema/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C856886F-C3B1-204E-8553-32BFADAC1628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91E1E71-337F-154D-87D4-BB59CE4C5716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6260" yWindow="3100" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{C9138D76-07EC-41C4-8817-AFCBF30C50C2}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="279">
   <si>
     <t>field_name</t>
   </si>
@@ -731,13 +731,157 @@
   </si>
   <si>
     <t>Sample Size Booster</t>
+  </si>
+  <si>
+    <t>Pre-recruit</t>
+  </si>
+  <si>
+    <t>sample_preparation</t>
+  </si>
+  <si>
+    <t>Chuẩn bị mẫu thử</t>
+  </si>
+  <si>
+    <t>usage_instructions</t>
+  </si>
+  <si>
+    <t>Chi tiết về cách sử dụng</t>
+  </si>
+  <si>
+    <t>sample_preparation_tasks</t>
+  </si>
+  <si>
+    <t>excel:sample_preparation_tasks</t>
+  </si>
+  <si>
+    <t>Chiết mẫu</t>
+  </si>
+  <si>
+    <t>Dán mẫu</t>
+  </si>
+  <si>
+    <t>sample_preparation_requirements</t>
+  </si>
+  <si>
+    <t>Các bước chuẩn bị mẫu</t>
+  </si>
+  <si>
+    <t>Chi tiết về cách chuẩn bị mẫu</t>
+  </si>
+  <si>
+    <t>material_procurement_requirements</t>
+  </si>
+  <si>
+    <t>Yêu cầu về mua vật dụng</t>
+  </si>
+  <si>
+    <t>Yêu cầu về chuyển mẫu</t>
+  </si>
+  <si>
+    <t>Có yêu cầu chuyển mẫu không?</t>
+  </si>
+  <si>
+    <t>sample_transfer_requirements</t>
+  </si>
+  <si>
+    <t>other_requirements</t>
+  </si>
+  <si>
+    <t>Các yêu cầu khác</t>
+  </si>
+  <si>
+    <t>is_unused_sample_returned</t>
+  </si>
+  <si>
+    <t>is_used_product_returned</t>
+  </si>
+  <si>
+    <t>Có thu hồi mẫu nguyên vẹn còn dư không?</t>
+  </si>
+  <si>
+    <t>Có thu hồi sản phẩm đã dùng không?</t>
+  </si>
+  <si>
+    <t>is_sample_transfer_required</t>
+  </si>
+  <si>
+    <t>is_diary_required</t>
+  </si>
+  <si>
+    <t>Có yêu cầu nhật ký không?</t>
+  </si>
+  <si>
+    <t>diary_type</t>
+  </si>
+  <si>
+    <t>Kênh lưu nhật ký</t>
+  </si>
+  <si>
+    <t>excel:diary_type</t>
+  </si>
+  <si>
+    <t>Paper</t>
+  </si>
+  <si>
+    <t>Nước ngọt</t>
+  </si>
+  <si>
+    <t>placement</t>
+  </si>
+  <si>
+    <t>screener</t>
+  </si>
+  <si>
+    <t>Screener</t>
+  </si>
+  <si>
+    <t>Placement</t>
+  </si>
+  <si>
+    <t>recall 1</t>
+  </si>
+  <si>
+    <t>recall 2</t>
+  </si>
+  <si>
+    <t>recall 3</t>
+  </si>
+  <si>
+    <t>recall 4</t>
+  </si>
+  <si>
+    <t>recall 5</t>
+  </si>
+  <si>
+    <t>Recall 1</t>
+  </si>
+  <si>
+    <t>Recall 2</t>
+  </si>
+  <si>
+    <t>Recall 3</t>
+  </si>
+  <si>
+    <t>Recall 4</t>
+  </si>
+  <si>
+    <t>Recall 5</t>
+  </si>
+  <si>
+    <t>Điều kiện khác</t>
+  </si>
+  <si>
+    <t>quota_requirements</t>
+  </si>
+  <si>
+    <t>Yêu cầu về Quota</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -748,6 +892,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1113,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6694FA44-4A7D-4629-A892-7DFDEEB80386}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -1402,19 +1552,19 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>112</v>
+        <v>232</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>233</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>113</v>
+        <v>232</v>
       </c>
       <c r="H14">
         <v>12</v>
@@ -1422,19 +1572,19 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B15" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H15">
         <v>12</v>
@@ -1442,10 +1592,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="B16" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>83</v>
@@ -1454,7 +1604,7 @@
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="H16">
         <v>12</v>
@@ -1462,10 +1612,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>83</v>
@@ -1474,7 +1624,7 @@
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="H17">
         <v>12</v>
@@ -1482,16 +1632,19 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>205</v>
+        <v>144</v>
       </c>
       <c r="B18" t="s">
-        <v>204</v>
+        <v>145</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="D18">
         <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>146</v>
       </c>
       <c r="H18">
         <v>12</v>
@@ -1499,19 +1652,16 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B19" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="D19">
         <v>1</v>
-      </c>
-      <c r="G19" t="s">
-        <v>203</v>
       </c>
       <c r="H19">
         <v>12</v>
@@ -1519,19 +1669,19 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
-      <c r="F20" t="s">
-        <v>222</v>
+      <c r="G20" t="s">
+        <v>203</v>
       </c>
       <c r="H20">
         <v>12</v>
@@ -1539,19 +1689,19 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="H21">
         <v>12</v>
@@ -1559,10 +1709,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B22" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>28</v>
@@ -1571,9 +1721,29 @@
         <v>1</v>
       </c>
       <c r="F22" t="s">
+        <v>207</v>
+      </c>
+      <c r="H22">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>212</v>
+      </c>
+      <c r="B23" t="s">
+        <v>213</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="F23" t="s">
         <v>215</v>
       </c>
-      <c r="H22">
+      <c r="H23">
         <v>12</v>
       </c>
     </row>
@@ -1585,15 +1755,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2B8FC54-75D4-4AC2-B92C-338AB72929A6}">
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1724,20 +1894,23 @@
         <v>163</v>
       </c>
       <c r="B6" t="s">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>183</v>
+        <v>20</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" s="1"/>
+      <c r="G6" t="s">
+        <v>77</v>
+      </c>
       <c r="H6" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -1745,52 +1918,54 @@
         <v>163</v>
       </c>
       <c r="B7" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C7" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>163</v>
+      <c r="A8" t="s">
+        <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>184</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>186</v>
+        <v>41</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
-      <c r="F8" s="1"/>
+      <c r="G8" t="s">
+        <v>82</v>
+      </c>
       <c r="H8" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>163</v>
+      <c r="A9" t="s">
+        <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>185</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>187</v>
+        <v>105</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>27</v>
@@ -1798,20 +1973,19 @@
       <c r="E9">
         <v>1</v>
       </c>
-      <c r="F9" s="1"/>
       <c r="H9" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>163</v>
+      <c r="A10" t="s">
+        <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>190</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>191</v>
+        <v>106</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>27</v>
@@ -1819,65 +1993,62 @@
       <c r="E10">
         <v>1</v>
       </c>
-      <c r="F10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>163</v>
+      <c r="A11" t="s">
+        <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
-      <c r="F11" s="1"/>
       <c r="G11" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>163</v>
+      <c r="A12" t="s">
+        <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>188</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
-      <c r="F12" s="1"/>
       <c r="H12" s="1" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>60</v>
@@ -1886,7 +2057,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>193</v>
@@ -1894,16 +2065,16 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1914,16 +2085,16 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1937,19 +2108,16 @@
         <v>63</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>248</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>276</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="E16">
         <v>1</v>
-      </c>
-      <c r="G16" t="s">
-        <v>86</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>193</v>
@@ -1960,13 +2128,13 @@
         <v>63</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1977,188 +2145,187 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>232</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>180</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>183</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
-      <c r="G18" t="s">
-        <v>94</v>
-      </c>
+      <c r="F18" s="1"/>
       <c r="H18" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>63</v>
+        <v>232</v>
       </c>
       <c r="B19" t="s">
-        <v>103</v>
+        <v>181</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>182</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
+      <c r="F19" s="1"/>
       <c r="H19" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>232</v>
       </c>
       <c r="B20" t="s">
-        <v>101</v>
+        <v>184</v>
       </c>
       <c r="C20" t="s">
-        <v>102</v>
+        <v>186</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
+      <c r="F20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>232</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>185</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>187</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
+      <c r="F21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>113</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>191</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
-      <c r="G22" t="s">
-        <v>114</v>
-      </c>
+      <c r="F22" s="1"/>
       <c r="H22" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>113</v>
+        <v>232</v>
       </c>
       <c r="B23" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C23" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
+      <c r="F23" s="1"/>
       <c r="H23" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>113</v>
+        <v>232</v>
       </c>
       <c r="B24" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="C24" t="s">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" t="s">
+        <v>51</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>118</v>
+        <v>232</v>
       </c>
       <c r="B25" t="s">
-        <v>135</v>
+        <v>257</v>
       </c>
       <c r="C25" t="s">
-        <v>119</v>
+        <v>258</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
+      <c r="F25" s="1"/>
       <c r="G25" t="s">
-        <v>120</v>
+        <v>259</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>118</v>
+        <v>232</v>
       </c>
       <c r="B26" t="s">
-        <v>136</v>
+        <v>236</v>
       </c>
       <c r="C26" t="s">
-        <v>126</v>
+        <v>241</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>60</v>
@@ -2166,22 +2333,23 @@
       <c r="E26">
         <v>1</v>
       </c>
+      <c r="F26" s="1"/>
       <c r="G26" t="s">
-        <v>127</v>
+        <v>237</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>133</v>
+        <v>232</v>
       </c>
       <c r="B27" t="s">
-        <v>141</v>
+        <v>240</v>
       </c>
       <c r="C27" t="s">
-        <v>134</v>
+        <v>242</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>57</v>
@@ -2189,59 +2357,65 @@
       <c r="E27">
         <v>1</v>
       </c>
+      <c r="F27" s="1"/>
       <c r="H27" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>133</v>
+        <v>232</v>
       </c>
       <c r="B28" t="s">
-        <v>137</v>
+        <v>243</v>
       </c>
       <c r="C28" t="s">
-        <v>138</v>
+        <v>244</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
+      <c r="F28" s="1"/>
       <c r="H28" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>133</v>
+        <v>232</v>
       </c>
       <c r="B29" t="s">
-        <v>142</v>
+        <v>254</v>
       </c>
       <c r="C29" t="s">
-        <v>139</v>
+        <v>246</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
+      <c r="F29" s="1"/>
+      <c r="G29" t="s">
+        <v>51</v>
+      </c>
       <c r="H29" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>133</v>
+        <v>232</v>
       </c>
       <c r="B30" t="s">
-        <v>143</v>
+        <v>247</v>
       </c>
       <c r="C30" t="s">
-        <v>140</v>
+        <v>245</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>57</v>
@@ -2249,42 +2423,41 @@
       <c r="E30">
         <v>1</v>
       </c>
+      <c r="F30" s="1"/>
       <c r="H30" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>146</v>
+        <v>232</v>
       </c>
       <c r="B31" t="s">
-        <v>147</v>
+        <v>248</v>
       </c>
       <c r="C31" t="s">
-        <v>149</v>
+        <v>249</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
-      <c r="G31" t="s">
-        <v>51</v>
-      </c>
+      <c r="F31" s="1"/>
       <c r="H31" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>146</v>
+        <v>232</v>
       </c>
       <c r="B32" t="s">
-        <v>148</v>
+        <v>250</v>
       </c>
       <c r="C32" t="s">
-        <v>150</v>
+        <v>252</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>23</v>
@@ -2292,51 +2465,56 @@
       <c r="E32">
         <v>1</v>
       </c>
+      <c r="F32" s="1"/>
       <c r="G32" t="s">
         <v>51</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>146</v>
+        <v>232</v>
       </c>
       <c r="B33" t="s">
-        <v>160</v>
+        <v>251</v>
       </c>
       <c r="C33" t="s">
-        <v>151</v>
+        <v>253</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
+      <c r="F33" s="1"/>
       <c r="G33" t="s">
-        <v>154</v>
+        <v>51</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="B34" t="s">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="C34" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E34">
         <v>1</v>
+      </c>
+      <c r="G34" t="s">
+        <v>114</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>193</v>
@@ -2344,19 +2522,22 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>222</v>
+        <v>113</v>
       </c>
       <c r="B35" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C35" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E35">
         <v>1</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>193</v>
@@ -2364,19 +2545,22 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>222</v>
+        <v>113</v>
       </c>
       <c r="B36" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C36" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>193</v>
@@ -2384,13 +2568,13 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>207</v>
+        <v>118</v>
       </c>
       <c r="B37" t="s">
-        <v>209</v>
+        <v>135</v>
       </c>
       <c r="C37" t="s">
-        <v>210</v>
+        <v>119</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>60</v>
@@ -2399,7 +2583,7 @@
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>193</v>
@@ -2407,19 +2591,22 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>207</v>
+        <v>118</v>
       </c>
       <c r="B38" t="s">
-        <v>208</v>
+        <v>136</v>
       </c>
       <c r="C38" t="s">
-        <v>219</v>
+        <v>126</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="E38">
         <v>1</v>
+      </c>
+      <c r="G38" t="s">
+        <v>127</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>193</v>
@@ -2427,16 +2614,16 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>207</v>
+        <v>118</v>
       </c>
       <c r="B39" t="s">
-        <v>211</v>
+        <v>277</v>
       </c>
       <c r="C39" t="s">
-        <v>189</v>
+        <v>278</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -2447,22 +2634,19 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>215</v>
+        <v>133</v>
       </c>
       <c r="B40" t="s">
-        <v>217</v>
+        <v>141</v>
       </c>
       <c r="C40" t="s">
-        <v>210</v>
+        <v>134</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E40">
         <v>1</v>
-      </c>
-      <c r="G40" t="s">
-        <v>114</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>193</v>
@@ -2470,13 +2654,13 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>215</v>
+        <v>133</v>
       </c>
       <c r="B41" t="s">
-        <v>216</v>
+        <v>137</v>
       </c>
       <c r="C41" t="s">
-        <v>219</v>
+        <v>138</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>27</v>
@@ -2490,21 +2674,296 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
+        <v>133</v>
+      </c>
+      <c r="B42" t="s">
+        <v>142</v>
+      </c>
+      <c r="C42" t="s">
+        <v>139</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>133</v>
+      </c>
+      <c r="B43" t="s">
+        <v>143</v>
+      </c>
+      <c r="C43" t="s">
+        <v>140</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>146</v>
+      </c>
+      <c r="B44" t="s">
+        <v>147</v>
+      </c>
+      <c r="C44" t="s">
+        <v>149</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="G44" t="s">
+        <v>51</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>146</v>
+      </c>
+      <c r="B45" t="s">
+        <v>148</v>
+      </c>
+      <c r="C45" t="s">
+        <v>150</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="G45" t="s">
+        <v>51</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>146</v>
+      </c>
+      <c r="B46" t="s">
+        <v>160</v>
+      </c>
+      <c r="C46" t="s">
+        <v>151</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+      <c r="G46" t="s">
+        <v>154</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>146</v>
+      </c>
+      <c r="B47" t="s">
+        <v>152</v>
+      </c>
+      <c r="C47" t="s">
+        <v>153</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>222</v>
+      </c>
+      <c r="B48" t="s">
+        <v>223</v>
+      </c>
+      <c r="C48" t="s">
+        <v>224</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>222</v>
+      </c>
+      <c r="B49" t="s">
+        <v>225</v>
+      </c>
+      <c r="C49" t="s">
+        <v>226</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>207</v>
+      </c>
+      <c r="B50" t="s">
+        <v>209</v>
+      </c>
+      <c r="C50" t="s">
+        <v>210</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+      <c r="G50" t="s">
+        <v>114</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>207</v>
+      </c>
+      <c r="B51" t="s">
+        <v>208</v>
+      </c>
+      <c r="C51" t="s">
+        <v>219</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>207</v>
+      </c>
+      <c r="B52" t="s">
+        <v>211</v>
+      </c>
+      <c r="C52" t="s">
+        <v>189</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
         <v>215</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B53" t="s">
+        <v>217</v>
+      </c>
+      <c r="C53" t="s">
+        <v>210</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="G53" t="s">
+        <v>114</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>215</v>
+      </c>
+      <c r="B54" t="s">
+        <v>216</v>
+      </c>
+      <c r="C54" t="s">
+        <v>219</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>215</v>
+      </c>
+      <c r="B55" t="s">
         <v>218</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C55" t="s">
         <v>189</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E42">
-        <v>1</v>
-      </c>
-      <c r="H42" s="1" t="s">
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="H55" s="1" t="s">
         <v>193</v>
       </c>
     </row>
@@ -2515,7 +2974,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{256469AD-8C25-494B-B7FC-7D7B2DDE1DC0}">
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -2668,445 +3127,611 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
+        <v>81</v>
+      </c>
+      <c r="B14" t="s">
+        <v>263</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
+        <v>81</v>
+      </c>
+      <c r="B15" t="s">
+        <v>262</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>265</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16">
-        <v>3</v>
+        <v>81</v>
+      </c>
+      <c r="B16" t="s">
+        <v>266</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>51</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
+        <v>81</v>
+      </c>
+      <c r="B17" t="s">
+        <v>267</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18">
-        <v>2</v>
+        <v>81</v>
+      </c>
+      <c r="B18" t="s">
+        <v>268</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>273</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>84</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
+        <v>81</v>
+      </c>
+      <c r="B19" t="s">
+        <v>269</v>
       </c>
       <c r="C19" t="s">
-        <v>87</v>
+        <v>274</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>84</v>
-      </c>
-      <c r="B20">
-        <v>2</v>
+        <v>81</v>
+      </c>
+      <c r="B20" t="s">
+        <v>270</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>275</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="B24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="B25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="B26">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B27">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="B31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C33" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="B35">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>155</v>
+        <v>121</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>156</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>155</v>
+        <v>121</v>
       </c>
       <c r="B37">
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>157</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>155</v>
+        <v>121</v>
       </c>
       <c r="B38">
         <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>158</v>
+        <v>124</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>155</v>
+        <v>121</v>
       </c>
       <c r="B39">
         <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>159</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>165</v>
+        <v>128</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>176</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>165</v>
+        <v>128</v>
       </c>
       <c r="B41">
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>178</v>
+        <v>130</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>165</v>
+        <v>128</v>
       </c>
       <c r="B42">
         <v>3</v>
       </c>
       <c r="C42" t="s">
-        <v>177</v>
+        <v>93</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>165</v>
+        <v>128</v>
       </c>
       <c r="B43">
         <v>4</v>
       </c>
       <c r="C43" t="s">
-        <v>179</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="B45">
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="B46">
         <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="B47">
         <v>4</v>
       </c>
       <c r="C47" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B48">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B49">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B50">
-        <v>9999</v>
+        <v>3</v>
       </c>
       <c r="C50" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C51" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>197</v>
+        <v>167</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>199</v>
+        <v>169</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
+        <v>167</v>
+      </c>
+      <c r="B53">
+        <v>2</v>
+      </c>
+      <c r="C53" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>167</v>
+      </c>
+      <c r="B54">
+        <v>3</v>
+      </c>
+      <c r="C54" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>167</v>
+      </c>
+      <c r="B55">
+        <v>4</v>
+      </c>
+      <c r="C55" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>167</v>
+      </c>
+      <c r="B56">
+        <v>5</v>
+      </c>
+      <c r="C56" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>167</v>
+      </c>
+      <c r="B57">
+        <v>6</v>
+      </c>
+      <c r="C57" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>167</v>
+      </c>
+      <c r="B58">
+        <v>7</v>
+      </c>
+      <c r="C58" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>167</v>
+      </c>
+      <c r="B59">
+        <v>9999</v>
+      </c>
+      <c r="C59" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
         <v>197</v>
       </c>
-      <c r="B53">
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>197</v>
+      </c>
+      <c r="B61">
+        <v>2</v>
+      </c>
+      <c r="C61" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>197</v>
+      </c>
+      <c r="B62">
         <v>3</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C62" t="s">
         <v>39</v>
       </c>
     </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>236</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="C63" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>236</v>
+      </c>
+      <c r="B64">
+        <v>2</v>
+      </c>
+      <c r="C64" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>257</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
+      <c r="C65" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>257</v>
+      </c>
+      <c r="B66">
+        <v>2</v>
+      </c>
+      <c r="C66" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>257</v>
+      </c>
+      <c r="B67">
+        <v>3</v>
+      </c>
+      <c r="C67" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>257</v>
+      </c>
+      <c r="B68">
+        <v>4</v>
+      </c>
+      <c r="C68" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/backend/storage/schema/quotation_template.xlsx
+++ b/backend/storage/schema/quotation_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/longlh123/Languages/GitHub/IPSOS-FINANCE-PAYMENT/backend/storage/schema/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91E1E71-337F-154D-87D4-BB59CE4C5716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C394AF-70E7-3243-9774-52639ED80C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6260" yWindow="3100" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{C9138D76-07EC-41C4-8817-AFCBF30C50C2}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="293">
   <si>
     <t>field_name</t>
   </si>
@@ -187,9 +187,6 @@
     <t>Other</t>
   </si>
   <si>
-    <t>range</t>
-  </si>
-  <si>
     <t>default_value</t>
   </si>
   <si>
@@ -875,6 +872,51 @@
   </si>
   <si>
     <t>Yêu cầu về Quota</t>
+  </si>
+  <si>
+    <t>project_conditions</t>
+  </si>
+  <si>
+    <t>Điều kiện dự án</t>
+  </si>
+  <si>
+    <t>project_conditions_config</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>Đối tượng</t>
+  </si>
+  <si>
+    <t>travel_required</t>
+  </si>
+  <si>
+    <t>Yêu cầu Travel</t>
+  </si>
+  <si>
+    <t>travel_required_config</t>
+  </si>
+  <si>
+    <t>area</t>
+  </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>excel:areas</t>
+  </si>
+  <si>
+    <t>areas</t>
+  </si>
+  <si>
+    <t>Urban</t>
+  </si>
+  <si>
+    <t>Rural</t>
+  </si>
+  <si>
+    <t>travel_comment</t>
   </si>
 </sst>
 </file>
@@ -1263,7 +1305,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6694FA44-4A7D-4629-A892-7DFDEEB80386}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -1289,27 +1331,27 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -1435,19 +1477,19 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H8">
         <v>12</v>
@@ -1461,7 +1503,7 @@
         <v>18</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1475,7 +1517,7 @@
         <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>23</v>
@@ -1484,7 +1526,7 @@
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H10">
         <v>12</v>
@@ -1492,19 +1534,19 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>161</v>
+      </c>
+      <c r="B11" t="s">
+        <v>160</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="B11" t="s">
-        <v>161</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>163</v>
       </c>
       <c r="H11">
         <v>12</v>
@@ -1512,10 +1554,10 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" t="s">
         <v>78</v>
-      </c>
-      <c r="B12" t="s">
-        <v>79</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>28</v>
@@ -1524,7 +1566,7 @@
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H12">
         <v>12</v>
@@ -1532,19 +1574,19 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
         <v>62</v>
-      </c>
-      <c r="B13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="F13" t="s">
-        <v>63</v>
       </c>
       <c r="H13">
         <v>12</v>
@@ -1552,19 +1594,16 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>232</v>
+        <v>278</v>
       </c>
       <c r="B14" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="F14" t="s">
-        <v>232</v>
+        <v>280</v>
       </c>
       <c r="H14">
         <v>12</v>
@@ -1572,19 +1611,19 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>112</v>
+        <v>231</v>
       </c>
       <c r="B15" t="s">
-        <v>111</v>
+        <v>232</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>113</v>
+        <v>231</v>
       </c>
       <c r="H15">
         <v>12</v>
@@ -1592,19 +1631,19 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B16" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="H16">
         <v>12</v>
@@ -1612,19 +1651,19 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="H17">
         <v>12</v>
@@ -1632,19 +1671,19 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="B18" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="H18">
         <v>12</v>
@@ -1652,16 +1691,19 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>205</v>
+        <v>143</v>
       </c>
       <c r="B19" t="s">
-        <v>204</v>
+        <v>144</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="D19">
         <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>145</v>
       </c>
       <c r="H19">
         <v>12</v>
@@ -1669,19 +1711,16 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="D20">
         <v>1</v>
-      </c>
-      <c r="G20" t="s">
-        <v>203</v>
       </c>
       <c r="H20">
         <v>12</v>
@@ -1689,19 +1728,19 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="B21" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
-      <c r="F21" t="s">
-        <v>222</v>
+      <c r="G21" t="s">
+        <v>202</v>
       </c>
       <c r="H21">
         <v>12</v>
@@ -1709,19 +1748,19 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="H22">
         <v>12</v>
@@ -1729,7 +1768,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="B23" t="s">
         <v>213</v>
@@ -1741,9 +1780,49 @@
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="H23">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>211</v>
+      </c>
+      <c r="B24" t="s">
+        <v>212</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s">
+        <v>214</v>
+      </c>
+      <c r="H24">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>283</v>
+      </c>
+      <c r="B25" t="s">
+        <v>284</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="F25" t="s">
+        <v>285</v>
+      </c>
+      <c r="H25">
         <v>12</v>
       </c>
     </row>
@@ -1755,7 +1834,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2B8FC54-75D4-4AC2-B92C-338AB72929A6}">
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.83203125" bestFit="1" customWidth="1"/>
@@ -1784,114 +1863,114 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C3" t="s">
         <v>194</v>
       </c>
-      <c r="C3" t="s">
-        <v>195</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" t="s">
         <v>163</v>
       </c>
-      <c r="B4" t="s">
-        <v>165</v>
-      </c>
-      <c r="C4" t="s">
-        <v>164</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C5" t="s">
         <v>167</v>
       </c>
-      <c r="C5" t="s">
-        <v>168</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B6" t="s">
         <v>45</v>
@@ -1900,72 +1979,72 @@
         <v>20</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C7" t="s">
         <v>188</v>
       </c>
-      <c r="C7" t="s">
-        <v>189</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" t="s">
         <v>80</v>
-      </c>
-      <c r="B8" t="s">
-        <v>81</v>
       </c>
       <c r="C8" t="s">
         <v>41</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>27</v>
@@ -1974,18 +2053,18 @@
         <v>1</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>27</v>
@@ -1994,182 +2073,181 @@
         <v>1</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>281</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>282</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
-      <c r="G11" t="s">
-        <v>86</v>
-      </c>
       <c r="H11" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
+      <c r="G12" t="s">
+        <v>85</v>
+      </c>
       <c r="H12" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
-      <c r="G13" t="s">
-        <v>94</v>
-      </c>
       <c r="H13" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>63</v>
+        <v>280</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
+      <c r="G14" t="s">
+        <v>93</v>
+      </c>
       <c r="H14" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>280</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>63</v>
+        <v>280</v>
       </c>
       <c r="B16" t="s">
-        <v>248</v>
+        <v>100</v>
       </c>
       <c r="C16" t="s">
-        <v>276</v>
+        <v>101</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>280</v>
       </c>
       <c r="B17" t="s">
-        <v>108</v>
+        <v>247</v>
       </c>
       <c r="C17" t="s">
-        <v>109</v>
+        <v>275</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>232</v>
+        <v>280</v>
       </c>
       <c r="B18" t="s">
-        <v>180</v>
+        <v>107</v>
       </c>
       <c r="C18" t="s">
-        <v>183</v>
+        <v>108</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
-      <c r="F18" s="1"/>
       <c r="H18" s="1" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B19" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C19" t="s">
         <v>182</v>
@@ -2182,18 +2260,18 @@
       </c>
       <c r="F19" s="1"/>
       <c r="H19" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B20" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C20" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>27</v>
@@ -2203,18 +2281,18 @@
       </c>
       <c r="F20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s">
+        <v>183</v>
+      </c>
+      <c r="C21" t="s">
         <v>185</v>
-      </c>
-      <c r="C21" t="s">
-        <v>187</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>27</v>
@@ -2224,18 +2302,18 @@
       </c>
       <c r="F21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C22" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>27</v>
@@ -2245,63 +2323,60 @@
       </c>
       <c r="F22" s="1"/>
       <c r="H22" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s">
-        <v>234</v>
+        <v>189</v>
       </c>
       <c r="C23" t="s">
-        <v>235</v>
+        <v>190</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23" s="1"/>
       <c r="H23" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="C24" t="s">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" s="1"/>
-      <c r="G24" t="s">
-        <v>51</v>
-      </c>
       <c r="H24" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B25" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C25" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>23</v>
@@ -2311,177 +2386,177 @@
       </c>
       <c r="F25" s="1"/>
       <c r="G25" t="s">
-        <v>259</v>
+        <v>50</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B26" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="C26" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B27" t="s">
+        <v>235</v>
+      </c>
+      <c r="C27" t="s">
         <v>240</v>
       </c>
-      <c r="C27" t="s">
-        <v>242</v>
-      </c>
       <c r="D27" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27" s="1"/>
+      <c r="G27" t="s">
+        <v>236</v>
+      </c>
       <c r="H27" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B28" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C28" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
       <c r="F28" s="1"/>
       <c r="H28" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B29" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C29" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29" s="1"/>
-      <c r="G29" t="s">
-        <v>51</v>
-      </c>
       <c r="H29" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B30" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C30" t="s">
         <v>245</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30" s="1"/>
+      <c r="G30" t="s">
+        <v>50</v>
+      </c>
       <c r="H30" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B31" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C31" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31" s="1"/>
       <c r="H31" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B32" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C32" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
       <c r="F32" s="1"/>
-      <c r="G32" t="s">
-        <v>51</v>
-      </c>
       <c r="H32" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B33" t="s">
+        <v>249</v>
+      </c>
+      <c r="C33" t="s">
         <v>251</v>
-      </c>
-      <c r="C33" t="s">
-        <v>253</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>23</v>
@@ -2491,259 +2566,260 @@
       </c>
       <c r="F33" s="1"/>
       <c r="G33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>113</v>
+        <v>231</v>
       </c>
       <c r="B34" t="s">
-        <v>110</v>
+        <v>250</v>
       </c>
       <c r="C34" t="s">
-        <v>115</v>
+        <v>252</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E34">
         <v>1</v>
       </c>
+      <c r="F34" s="1"/>
       <c r="G34" t="s">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
+        <v>112</v>
+      </c>
+      <c r="B35" t="s">
+        <v>109</v>
+      </c>
+      <c r="C35" t="s">
+        <v>114</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="G35" t="s">
         <v>113</v>
       </c>
-      <c r="B35" t="s">
-        <v>227</v>
-      </c>
-      <c r="C35" t="s">
-        <v>229</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E35">
-        <v>1</v>
-      </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
       <c r="H35" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B36" t="s">
+        <v>226</v>
+      </c>
+      <c r="C36" t="s">
         <v>228</v>
-      </c>
-      <c r="C36" t="s">
-        <v>230</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36">
         <v>0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B37" t="s">
-        <v>135</v>
+        <v>227</v>
       </c>
       <c r="C37" t="s">
-        <v>119</v>
+        <v>229</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="E37">
-        <v>1</v>
-      </c>
-      <c r="G37" t="s">
-        <v>120</v>
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
+        <v>117</v>
+      </c>
+      <c r="B38" t="s">
+        <v>134</v>
+      </c>
+      <c r="C38" t="s">
         <v>118</v>
       </c>
-      <c r="B38" t="s">
-        <v>136</v>
-      </c>
-      <c r="C38" t="s">
-        <v>126</v>
-      </c>
       <c r="D38" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B39" t="s">
-        <v>277</v>
+        <v>135</v>
       </c>
       <c r="C39" t="s">
-        <v>278</v>
+        <v>125</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
+      <c r="G39" t="s">
+        <v>126</v>
+      </c>
       <c r="H39" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="B40" t="s">
-        <v>141</v>
+        <v>276</v>
       </c>
       <c r="C40" t="s">
-        <v>134</v>
+        <v>277</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E40">
         <v>1</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
+        <v>132</v>
+      </c>
+      <c r="B41" t="s">
+        <v>140</v>
+      </c>
+      <c r="C41" t="s">
         <v>133</v>
       </c>
-      <c r="B41" t="s">
-        <v>137</v>
-      </c>
-      <c r="C41" t="s">
-        <v>138</v>
-      </c>
       <c r="D41" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E41">
         <v>1</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B42" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C42" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B43" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C43" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E43">
         <v>1</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="B44" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C44" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="E44">
         <v>1</v>
       </c>
-      <c r="G44" t="s">
-        <v>51</v>
-      </c>
       <c r="H44" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
+        <v>145</v>
+      </c>
+      <c r="B45" t="s">
         <v>146</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>148</v>
-      </c>
-      <c r="C45" t="s">
-        <v>150</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>23</v>
@@ -2752,219 +2828,308 @@
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B46" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="C46" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E46">
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B47" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C47" t="s">
+        <v>150</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="G47" t="s">
         <v>153</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E47">
-        <v>1</v>
-      </c>
       <c r="H47" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>222</v>
+        <v>145</v>
       </c>
       <c r="B48" t="s">
-        <v>223</v>
+        <v>151</v>
       </c>
       <c r="C48" t="s">
-        <v>224</v>
+        <v>152</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E48">
         <v>1</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
+        <v>221</v>
+      </c>
+      <c r="B49" t="s">
         <v>222</v>
       </c>
-      <c r="B49" t="s">
-        <v>225</v>
-      </c>
       <c r="C49" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E49">
         <v>1</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="B50" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="C50" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E50">
         <v>1</v>
       </c>
-      <c r="G50" t="s">
-        <v>114</v>
-      </c>
       <c r="H50" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B51" t="s">
         <v>208</v>
       </c>
       <c r="C51" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="E51">
         <v>1</v>
       </c>
+      <c r="G51" t="s">
+        <v>113</v>
+      </c>
       <c r="H51" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>206</v>
+      </c>
+      <c r="B52" t="s">
         <v>207</v>
       </c>
-      <c r="B52" t="s">
-        <v>211</v>
-      </c>
       <c r="C52" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B53" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C53" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="E53">
         <v>1</v>
       </c>
-      <c r="G53" t="s">
-        <v>114</v>
-      </c>
       <c r="H53" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B54" t="s">
         <v>216</v>
       </c>
       <c r="C54" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="E54">
         <v>1</v>
       </c>
+      <c r="G54" t="s">
+        <v>113</v>
+      </c>
       <c r="H54" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B55" t="s">
         <v>215</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>218</v>
       </c>
-      <c r="C55" t="s">
-        <v>189</v>
-      </c>
       <c r="D55" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>214</v>
+      </c>
+      <c r="B56" t="s">
+        <v>217</v>
+      </c>
+      <c r="C56" t="s">
+        <v>188</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E55">
-        <v>1</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>193</v>
+      <c r="E56">
+        <v>1</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>285</v>
+      </c>
+      <c r="B57" t="s">
+        <v>109</v>
+      </c>
+      <c r="C57" t="s">
+        <v>114</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+      <c r="G57" t="s">
+        <v>113</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>285</v>
+      </c>
+      <c r="B58" t="s">
+        <v>286</v>
+      </c>
+      <c r="C58" t="s">
+        <v>287</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+      <c r="G58" t="s">
+        <v>288</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>285</v>
+      </c>
+      <c r="B59" t="s">
+        <v>292</v>
+      </c>
+      <c r="C59" t="s">
+        <v>188</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -2974,7 +3139,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{256469AD-8C25-494B-B7FC-7D7B2DDE1DC0}">
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -3053,7 +3218,7 @@
         <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
         <v>36</v>
@@ -3064,7 +3229,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
         <v>37</v>
@@ -3075,7 +3240,7 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
         <v>38</v>
@@ -3086,7 +3251,7 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
         <v>39</v>
@@ -3094,10 +3259,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
         <v>42</v>
@@ -3105,10 +3270,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
         <v>43</v>
@@ -3116,10 +3281,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
         <v>44</v>
@@ -3127,79 +3292,79 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B14" t="s">
+        <v>262</v>
+      </c>
+      <c r="C14" t="s">
         <v>263</v>
-      </c>
-      <c r="C14" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B16" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C16" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B17" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C17" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B18" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C18" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B19" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C19" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C20" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -3232,7 +3397,7 @@
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -3248,414 +3413,414 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
         <v>51</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B26">
         <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B29">
         <v>3</v>
       </c>
       <c r="C29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B32">
         <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B33">
         <v>4</v>
       </c>
       <c r="C33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B34">
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B35">
         <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
+        <v>120</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
         <v>121</v>
-      </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-      <c r="C36" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B37">
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B38">
         <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B39">
         <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
+        <v>127</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
         <v>128</v>
-      </c>
-      <c r="B40">
-        <v>1</v>
-      </c>
-      <c r="C40" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B41">
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B42">
         <v>3</v>
       </c>
       <c r="C42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B43">
         <v>4</v>
       </c>
       <c r="C43" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
+        <v>154</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
         <v>155</v>
-      </c>
-      <c r="B44">
-        <v>1</v>
-      </c>
-      <c r="C44" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B45">
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B46">
         <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B47">
         <v>4</v>
       </c>
       <c r="C47" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B48">
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B49">
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B50">
         <v>3</v>
       </c>
       <c r="C50" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B51">
         <v>4</v>
       </c>
       <c r="C51" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B52">
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B53">
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B54">
         <v>3</v>
       </c>
       <c r="C54" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B55">
         <v>4</v>
       </c>
       <c r="C55" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B56">
         <v>5</v>
       </c>
       <c r="C56" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B57">
         <v>6</v>
       </c>
       <c r="C57" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B58">
         <v>7</v>
       </c>
       <c r="C58" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B59">
         <v>9999</v>
       </c>
       <c r="C59" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
+        <v>196</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60" t="s">
         <v>197</v>
-      </c>
-      <c r="B60">
-        <v>1</v>
-      </c>
-      <c r="C60" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B61">
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B62">
         <v>3</v>
@@ -3666,40 +3831,40 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B63">
         <v>1</v>
       </c>
       <c r="C63" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B64">
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B65">
         <v>1</v>
       </c>
       <c r="C65" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B66">
         <v>2</v>
@@ -3710,7 +3875,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B67">
         <v>3</v>
@@ -3721,13 +3886,35 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B68">
         <v>4</v>
       </c>
       <c r="C68" t="s">
         <v>48</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>289</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
+      </c>
+      <c r="C69" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>289</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
+      </c>
+      <c r="C70" t="s">
+        <v>291</v>
       </c>
     </row>
   </sheetData>

--- a/backend/storage/schema/quotation_template.xlsx
+++ b/backend/storage/schema/quotation_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/longlh123/Languages/GitHub/IPSOS-FINANCE-PAYMENT/backend/storage/schema/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C394AF-70E7-3243-9774-52639ED80C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F8F6FF6-8A0E-F640-ABDF-5B152D6CF046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6260" yWindow="3100" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{C9138D76-07EC-41C4-8817-AFCBF30C50C2}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="295">
   <si>
     <t>field_name</t>
   </si>
@@ -520,9 +520,6 @@
     <t>dp_data_processing</t>
   </si>
   <si>
-    <t>Phương Pháp</t>
-  </si>
-  <si>
     <t>fieldwork_design</t>
   </si>
   <si>
@@ -538,33 +535,9 @@
     <t>excel:research_type</t>
   </si>
   <si>
-    <t>product_type</t>
-  </si>
-  <si>
     <t>Sản phẩm nghiên cứu</t>
   </si>
   <si>
-    <t>Nước giặt</t>
-  </si>
-  <si>
-    <t>Bột giặt</t>
-  </si>
-  <si>
-    <t>Nước rửa chén</t>
-  </si>
-  <si>
-    <t>Nước xả vải</t>
-  </si>
-  <si>
-    <t>Thuốc lá</t>
-  </si>
-  <si>
-    <t>Bia</t>
-  </si>
-  <si>
-    <t>excel:product_type</t>
-  </si>
-  <si>
     <t>Product Test - Monadic</t>
   </si>
   <si>
@@ -637,9 +610,6 @@
     <t>Tablet &lt; 9 inch</t>
   </si>
   <si>
-    <t>Không yêu cầu</t>
-  </si>
-  <si>
     <t>pm_required</t>
   </si>
   <si>
@@ -820,9 +790,6 @@
     <t>Paper</t>
   </si>
   <si>
-    <t>Nước ngọt</t>
-  </si>
-  <si>
     <t>placement</t>
   </si>
   <si>
@@ -917,6 +884,45 @@
   </si>
   <si>
     <t>travel_comment</t>
+  </si>
+  <si>
+    <t>Phương pháp nghiên cứu</t>
+  </si>
+  <si>
+    <t>product_classification</t>
+  </si>
+  <si>
+    <t>industry</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>subcategory</t>
+  </si>
+  <si>
+    <t>Ngành hàng</t>
+  </si>
+  <si>
+    <t>Nhóm sản phẩm</t>
+  </si>
+  <si>
+    <t>Loại sản phẩm</t>
+  </si>
+  <si>
+    <t>product_classification_config</t>
+  </si>
+  <si>
+    <t>db:industries</t>
+  </si>
+  <si>
+    <t>db:categories</t>
+  </si>
+  <si>
+    <t>db:subcategories</t>
+  </si>
+  <si>
+    <t>single-select</t>
   </si>
 </sst>
 </file>
@@ -1305,7 +1311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6694FA44-4A7D-4629-A892-7DFDEEB80386}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -1483,7 +1489,7 @@
         <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>59</v>
+        <v>294</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1534,10 +1540,10 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B11" t="s">
-        <v>160</v>
+        <v>282</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>82</v>
@@ -1546,7 +1552,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H11">
         <v>12</v>
@@ -1554,19 +1560,19 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>77</v>
+        <v>283</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="H12">
         <v>12</v>
@@ -1574,10 +1580,10 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>28</v>
@@ -1586,7 +1592,7 @@
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="H13">
         <v>12</v>
@@ -1594,16 +1600,19 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>278</v>
+        <v>61</v>
       </c>
       <c r="B14" t="s">
-        <v>279</v>
+        <v>60</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>82</v>
+        <v>28</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>280</v>
+        <v>62</v>
       </c>
       <c r="H14">
         <v>12</v>
@@ -1611,10 +1620,10 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>231</v>
+        <v>267</v>
       </c>
       <c r="B15" t="s">
-        <v>232</v>
+        <v>268</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>82</v>
@@ -1623,7 +1632,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>231</v>
+        <v>269</v>
       </c>
       <c r="H15">
         <v>12</v>
@@ -1631,19 +1640,19 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>111</v>
+        <v>221</v>
       </c>
       <c r="B16" t="s">
-        <v>110</v>
+        <v>222</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>112</v>
+        <v>221</v>
       </c>
       <c r="H16">
         <v>12</v>
@@ -1651,19 +1660,19 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B17" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="H17">
         <v>12</v>
@@ -1671,10 +1680,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B18" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>82</v>
@@ -1683,7 +1692,7 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="H18">
         <v>12</v>
@@ -1691,10 +1700,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="B19" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>82</v>
@@ -1703,7 +1712,7 @@
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="H19">
         <v>12</v>
@@ -1711,16 +1720,19 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>204</v>
+        <v>143</v>
       </c>
       <c r="B20" t="s">
-        <v>203</v>
+        <v>144</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="D20">
         <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>145</v>
       </c>
       <c r="H20">
         <v>12</v>
@@ -1728,19 +1740,16 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B21" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="D21">
         <v>1</v>
-      </c>
-      <c r="G21" t="s">
-        <v>202</v>
       </c>
       <c r="H21">
         <v>12</v>
@@ -1748,19 +1757,19 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="B22" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
-      <c r="F22" t="s">
-        <v>221</v>
+      <c r="G22" t="s">
+        <v>192</v>
       </c>
       <c r="H22">
         <v>12</v>
@@ -1768,19 +1777,19 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B23" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H23">
         <v>12</v>
@@ -1788,10 +1797,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="B24" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>28</v>
@@ -1800,7 +1809,7 @@
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="H24">
         <v>12</v>
@@ -1808,10 +1817,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>283</v>
+        <v>201</v>
       </c>
       <c r="B25" t="s">
-        <v>284</v>
+        <v>202</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>28</v>
@@ -1820,9 +1829,29 @@
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>285</v>
+        <v>204</v>
       </c>
       <c r="H25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>272</v>
+      </c>
+      <c r="B26" t="s">
+        <v>273</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="F26" t="s">
+        <v>274</v>
+      </c>
+      <c r="H26">
         <v>12</v>
       </c>
     </row>
@@ -1834,13 +1863,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2B8FC54-75D4-4AC2-B92C-338AB72929A6}">
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
@@ -1874,7 +1903,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
@@ -1893,18 +1922,18 @@
         <v>67</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>59</v>
@@ -1914,21 +1943,21 @@
       </c>
       <c r="F3" s="1"/>
       <c r="G3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" t="s">
         <v>162</v>
-      </c>
-      <c r="B4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C4" t="s">
-        <v>163</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>59</v>
@@ -1938,21 +1967,21 @@
       </c>
       <c r="F4" s="1"/>
       <c r="G4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>59</v>
@@ -1962,98 +1991,103 @@
       </c>
       <c r="F5" s="1"/>
       <c r="G5" t="s">
-        <v>174</v>
+        <v>76</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>178</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>179</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" t="s">
-        <v>76</v>
-      </c>
       <c r="H6" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>162</v>
+      <c r="A7" t="s">
+        <v>290</v>
       </c>
       <c r="B7" t="s">
-        <v>187</v>
+        <v>284</v>
       </c>
       <c r="C7" t="s">
-        <v>188</v>
+        <v>287</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>56</v>
+        <v>294</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7" s="1"/>
+      <c r="G7" t="s">
+        <v>291</v>
+      </c>
       <c r="H7" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>285</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>288</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>59</v>
+        <v>294</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
+      <c r="F8" s="1"/>
       <c r="G8" t="s">
-        <v>81</v>
+        <v>292</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>286</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>289</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
+      <c r="F9" s="1"/>
+      <c r="G9" t="s">
+        <v>293</v>
+      </c>
       <c r="H9" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -2061,62 +2095,62 @@
         <v>79</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>41</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>27</v>
+        <v>294</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
+      <c r="G10" t="s">
+        <v>81</v>
+      </c>
       <c r="H10" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="B11" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>282</v>
+        <v>104</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
-      <c r="G12" t="s">
-        <v>85</v>
-      </c>
       <c r="H12" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -2124,10 +2158,10 @@
         <v>62</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>270</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>271</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>6</v>
@@ -2136,81 +2170,84 @@
         <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>280</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>59</v>
+        <v>294</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>280</v>
+        <v>62</v>
       </c>
       <c r="B15" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="B16" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
+      <c r="G16" t="s">
+        <v>93</v>
+      </c>
       <c r="H16" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="B17" t="s">
-        <v>247</v>
+        <v>102</v>
       </c>
       <c r="C17" t="s">
-        <v>275</v>
+        <v>103</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>56</v>
@@ -2219,18 +2256,18 @@
         <v>1</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="B18" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>56</v>
@@ -2239,60 +2276,58 @@
         <v>1</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>231</v>
+        <v>269</v>
       </c>
       <c r="B19" t="s">
-        <v>179</v>
+        <v>237</v>
       </c>
       <c r="C19" t="s">
-        <v>182</v>
+        <v>264</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
-      <c r="F19" s="1"/>
       <c r="H19" s="1" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>231</v>
+        <v>269</v>
       </c>
       <c r="B20" t="s">
-        <v>180</v>
+        <v>107</v>
       </c>
       <c r="C20" t="s">
-        <v>181</v>
+        <v>108</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
-      <c r="F20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B21" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="C21" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>27</v>
@@ -2302,18 +2337,18 @@
       </c>
       <c r="F21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B22" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="C22" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>27</v>
@@ -2323,18 +2358,18 @@
       </c>
       <c r="F22" s="1"/>
       <c r="H22" s="1" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="C23" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>27</v>
@@ -2344,177 +2379,174 @@
       </c>
       <c r="F23" s="1"/>
       <c r="H23" s="1" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B24" t="s">
-        <v>233</v>
+        <v>175</v>
       </c>
       <c r="C24" t="s">
-        <v>234</v>
+        <v>177</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" s="1"/>
       <c r="H24" s="1" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B25" t="s">
-        <v>254</v>
+        <v>180</v>
       </c>
       <c r="C25" t="s">
-        <v>255</v>
+        <v>181</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25" s="1"/>
-      <c r="G25" t="s">
-        <v>50</v>
-      </c>
       <c r="H25" s="1" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B26" t="s">
-        <v>256</v>
+        <v>223</v>
       </c>
       <c r="C26" t="s">
-        <v>257</v>
+        <v>224</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26" s="1"/>
-      <c r="G26" t="s">
-        <v>258</v>
-      </c>
       <c r="H26" s="1" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B27" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C27" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" t="s">
-        <v>236</v>
+        <v>50</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B28" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="C28" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
       <c r="F28" s="1"/>
+      <c r="G28" t="s">
+        <v>248</v>
+      </c>
       <c r="H28" s="1" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B29" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="C29" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29" s="1"/>
+      <c r="G29" t="s">
+        <v>226</v>
+      </c>
       <c r="H29" s="1" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>221</v>
+      </c>
+      <c r="B30" t="s">
+        <v>229</v>
+      </c>
+      <c r="C30" t="s">
         <v>231</v>
       </c>
-      <c r="B30" t="s">
-        <v>253</v>
-      </c>
-      <c r="C30" t="s">
-        <v>245</v>
-      </c>
       <c r="D30" s="1" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30" s="1"/>
-      <c r="G30" t="s">
-        <v>50</v>
-      </c>
       <c r="H30" s="1" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B31" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C31" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>56</v>
@@ -2524,122 +2556,121 @@
       </c>
       <c r="F31" s="1"/>
       <c r="H31" s="1" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B32" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C32" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
       <c r="F32" s="1"/>
+      <c r="G32" t="s">
+        <v>50</v>
+      </c>
       <c r="H32" s="1" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B33" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="C33" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33" s="1"/>
-      <c r="G33" t="s">
-        <v>50</v>
-      </c>
       <c r="H33" s="1" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B34" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="C34" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="E34">
         <v>1</v>
       </c>
       <c r="F34" s="1"/>
-      <c r="G34" t="s">
-        <v>50</v>
-      </c>
       <c r="H34" s="1" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>112</v>
+        <v>221</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>239</v>
       </c>
       <c r="C35" t="s">
-        <v>114</v>
+        <v>241</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
+      <c r="F35" s="1"/>
       <c r="G35" t="s">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>112</v>
+        <v>221</v>
       </c>
       <c r="B36" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="C36" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E36">
         <v>1</v>
       </c>
-      <c r="F36">
-        <v>0</v>
+      <c r="F36" s="1"/>
+      <c r="G36" t="s">
+        <v>50</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -2647,68 +2678,68 @@
         <v>112</v>
       </c>
       <c r="B37" t="s">
-        <v>227</v>
+        <v>109</v>
       </c>
       <c r="C37" t="s">
-        <v>229</v>
+        <v>114</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>27</v>
+        <v>294</v>
       </c>
       <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G37" t="s">
+        <v>113</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B38" t="s">
-        <v>134</v>
+        <v>216</v>
       </c>
       <c r="C38" t="s">
-        <v>118</v>
+        <v>218</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
-      <c r="G38" t="s">
-        <v>119</v>
+      <c r="F38">
+        <v>0</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B39" t="s">
-        <v>135</v>
+        <v>217</v>
       </c>
       <c r="C39" t="s">
-        <v>125</v>
+        <v>219</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="E39">
-        <v>1</v>
-      </c>
-      <c r="G39" t="s">
-        <v>126</v>
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -2716,59 +2747,65 @@
         <v>117</v>
       </c>
       <c r="B40" t="s">
-        <v>276</v>
+        <v>134</v>
       </c>
       <c r="C40" t="s">
-        <v>277</v>
+        <v>118</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>56</v>
+        <v>294</v>
       </c>
       <c r="E40">
         <v>1</v>
       </c>
+      <c r="G40" t="s">
+        <v>119</v>
+      </c>
       <c r="H40" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="B41" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C41" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E41">
         <v>1</v>
       </c>
+      <c r="G41" t="s">
+        <v>126</v>
+      </c>
       <c r="H41" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="B42" t="s">
-        <v>136</v>
+        <v>265</v>
       </c>
       <c r="C42" t="s">
-        <v>137</v>
+        <v>266</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -2776,10 +2813,10 @@
         <v>132</v>
       </c>
       <c r="B43" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C43" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>56</v>
@@ -2788,7 +2825,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -2796,65 +2833,59 @@
         <v>132</v>
       </c>
       <c r="B44" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C44" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="E44">
         <v>1</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="B45" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C45" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="E45">
         <v>1</v>
       </c>
-      <c r="G45" t="s">
-        <v>50</v>
-      </c>
       <c r="H45" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="B46" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C46" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="E46">
         <v>1</v>
       </c>
-      <c r="G46" t="s">
-        <v>50</v>
-      </c>
       <c r="H46" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -2862,22 +2893,22 @@
         <v>145</v>
       </c>
       <c r="B47" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="C47" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="E47">
         <v>1</v>
       </c>
       <c r="G47" t="s">
-        <v>153</v>
+        <v>50</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -2885,50 +2916,56 @@
         <v>145</v>
       </c>
       <c r="B48" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C48" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="E48">
         <v>1</v>
       </c>
+      <c r="G48" t="s">
+        <v>50</v>
+      </c>
       <c r="H48" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>221</v>
+        <v>145</v>
       </c>
       <c r="B49" t="s">
-        <v>222</v>
+        <v>159</v>
       </c>
       <c r="C49" t="s">
-        <v>223</v>
+        <v>150</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E49">
         <v>1</v>
       </c>
+      <c r="G49" t="s">
+        <v>153</v>
+      </c>
       <c r="H49" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>221</v>
+        <v>145</v>
       </c>
       <c r="B50" t="s">
-        <v>224</v>
+        <v>151</v>
       </c>
       <c r="C50" t="s">
-        <v>225</v>
+        <v>152</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>56</v>
@@ -2937,209 +2974,250 @@
         <v>1</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B51" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C51" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E51">
         <v>1</v>
       </c>
-      <c r="G51" t="s">
-        <v>113</v>
-      </c>
       <c r="H51" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B52" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C52" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B53" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="C53" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>6</v>
+        <v>294</v>
       </c>
       <c r="E53">
         <v>1</v>
       </c>
+      <c r="G53" t="s">
+        <v>113</v>
+      </c>
       <c r="H53" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="B54" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="C54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="E54">
         <v>1</v>
       </c>
-      <c r="G54" t="s">
-        <v>113</v>
-      </c>
       <c r="H54" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="B55" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="C55" t="s">
-        <v>218</v>
+        <v>179</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E55">
         <v>1</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="B56" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="C56" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>6</v>
+        <v>294</v>
       </c>
       <c r="E56">
         <v>1</v>
       </c>
+      <c r="G56" t="s">
+        <v>113</v>
+      </c>
       <c r="H56" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>285</v>
+        <v>204</v>
       </c>
       <c r="B57" t="s">
-        <v>109</v>
+        <v>205</v>
       </c>
       <c r="C57" t="s">
-        <v>114</v>
+        <v>208</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="E57">
         <v>1</v>
       </c>
-      <c r="G57" t="s">
-        <v>113</v>
-      </c>
       <c r="H57" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>285</v>
+        <v>204</v>
       </c>
       <c r="B58" t="s">
-        <v>286</v>
+        <v>207</v>
       </c>
       <c r="C58" t="s">
-        <v>287</v>
+        <v>179</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="E58">
         <v>1</v>
       </c>
-      <c r="G58" t="s">
-        <v>288</v>
-      </c>
       <c r="H58" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="B59" t="s">
-        <v>292</v>
+        <v>109</v>
       </c>
       <c r="C59" t="s">
-        <v>188</v>
+        <v>114</v>
       </c>
       <c r="D59" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="G59" t="s">
+        <v>113</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>274</v>
+      </c>
+      <c r="B60" t="s">
+        <v>275</v>
+      </c>
+      <c r="C60" t="s">
+        <v>276</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+      <c r="G60" t="s">
+        <v>277</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>274</v>
+      </c>
+      <c r="B61" t="s">
+        <v>281</v>
+      </c>
+      <c r="C61" t="s">
+        <v>179</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E59">
-        <v>1</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>192</v>
+      <c r="E61">
+        <v>1</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{256469AD-8C25-494B-B7FC-7D7B2DDE1DC0}">
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -3295,10 +3373,10 @@
         <v>80</v>
       </c>
       <c r="B14" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="C14" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -3306,10 +3384,10 @@
         <v>80</v>
       </c>
       <c r="B15" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="C15" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -3317,10 +3395,10 @@
         <v>80</v>
       </c>
       <c r="B16" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="C16" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -3328,10 +3406,10 @@
         <v>80</v>
       </c>
       <c r="B17" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="C17" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -3339,10 +3417,10 @@
         <v>80</v>
       </c>
       <c r="B18" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="C18" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -3350,10 +3428,10 @@
         <v>80</v>
       </c>
       <c r="B19" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="C19" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -3361,10 +3439,10 @@
         <v>80</v>
       </c>
       <c r="B20" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="C20" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -3397,7 +3475,7 @@
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -3666,255 +3744,167 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B48">
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B49">
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B50">
         <v>3</v>
       </c>
       <c r="C50" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B51">
         <v>4</v>
       </c>
       <c r="C51" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="B52">
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="B53">
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="B54">
         <v>3</v>
       </c>
       <c r="C54" t="s">
-        <v>170</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>166</v>
+        <v>225</v>
       </c>
       <c r="B55">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C55" t="s">
-        <v>171</v>
+        <v>227</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>166</v>
+        <v>225</v>
       </c>
       <c r="B56">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>172</v>
+        <v>228</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>166</v>
+        <v>246</v>
       </c>
       <c r="B57">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>173</v>
+        <v>249</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>166</v>
+        <v>246</v>
       </c>
       <c r="B58">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>260</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>166</v>
+        <v>246</v>
       </c>
       <c r="B59">
-        <v>9999</v>
+        <v>3</v>
       </c>
       <c r="C59" t="s">
-        <v>199</v>
+        <v>36</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>196</v>
+        <v>246</v>
       </c>
       <c r="B60">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C60" t="s">
-        <v>197</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>196</v>
+        <v>278</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61" t="s">
-        <v>198</v>
+        <v>279</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>196</v>
+        <v>278</v>
       </c>
       <c r="B62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>235</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
-      </c>
-      <c r="C63" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>235</v>
-      </c>
-      <c r="B64">
-        <v>2</v>
-      </c>
-      <c r="C64" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>256</v>
-      </c>
-      <c r="B65">
-        <v>1</v>
-      </c>
-      <c r="C65" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>256</v>
-      </c>
-      <c r="B66">
-        <v>2</v>
-      </c>
-      <c r="C66" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>256</v>
-      </c>
-      <c r="B67">
-        <v>3</v>
-      </c>
-      <c r="C67" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>256</v>
-      </c>
-      <c r="B68">
-        <v>4</v>
-      </c>
-      <c r="C68" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>289</v>
-      </c>
-      <c r="B69">
-        <v>1</v>
-      </c>
-      <c r="C69" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>289</v>
-      </c>
-      <c r="B70">
-        <v>2</v>
-      </c>
-      <c r="C70" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>

--- a/backend/storage/schema/quotation_template.xlsx
+++ b/backend/storage/schema/quotation_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/longlh123/Languages/GitHub/IPSOS-FINANCE-PAYMENT/backend/storage/schema/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F8F6FF6-8A0E-F640-ABDF-5B152D6CF046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C82794-2C6F-AC46-851E-F0BE86B4F9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6260" yWindow="3100" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{C9138D76-07EC-41C4-8817-AFCBF30C50C2}"/>
+    <workbookView xWindow="6260" yWindow="3100" windowWidth="29040" windowHeight="17520" xr2:uid="{C9138D76-07EC-41C4-8817-AFCBF30C50C2}"/>
   </bookViews>
   <sheets>
     <sheet name="FIELDS" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="298">
   <si>
     <t>field_name</t>
   </si>
@@ -850,9 +850,6 @@
     <t>project_conditions_config</t>
   </si>
   <si>
-    <t>description</t>
-  </si>
-  <si>
     <t>Đối tượng</t>
   </si>
   <si>
@@ -923,6 +920,18 @@
   </si>
   <si>
     <t>single-select</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>Urban / Rural</t>
+  </si>
+  <si>
+    <t>target_audience</t>
   </si>
 </sst>
 </file>
@@ -1311,7 +1320,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6694FA44-4A7D-4629-A892-7DFDEEB80386}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -1320,10 +1329,11 @@
     <col min="4" max="4" width="8.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="84.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.5" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1354,8 +1364,11 @@
       <c r="J1" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K1" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -1375,8 +1388,11 @@
       <c r="I2">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K2" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1395,8 +1411,11 @@
       <c r="I3">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K3" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1418,8 +1437,11 @@
       <c r="I4">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K4" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1440,8 +1462,11 @@
       <c r="I5">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K5" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1460,8 +1485,11 @@
       <c r="I6">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K6" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1480,8 +1508,11 @@
       <c r="I7">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K7" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>74</v>
       </c>
@@ -1489,7 +1520,7 @@
         <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1500,8 +1531,11 @@
       <c r="H8">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K8" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1517,8 +1551,11 @@
       <c r="H9">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K9" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -1537,13 +1574,16 @@
       <c r="H10">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K10" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>160</v>
       </c>
       <c r="B11" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>82</v>
@@ -1557,10 +1597,13 @@
       <c r="H11">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K11" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B12" t="s">
         <v>165</v>
@@ -1572,13 +1615,16 @@
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H12">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K12" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>77</v>
       </c>
@@ -1597,8 +1643,11 @@
       <c r="H13">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K13" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>61</v>
       </c>
@@ -1617,8 +1666,11 @@
       <c r="H14">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K14" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>267</v>
       </c>
@@ -1637,48 +1689,57 @@
       <c r="H15">
         <v>12</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K15" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>221</v>
+        <v>111</v>
       </c>
       <c r="B16" t="s">
-        <v>222</v>
+        <v>110</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>221</v>
+        <v>112</v>
       </c>
       <c r="H16">
         <v>12</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="K16" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>221</v>
       </c>
       <c r="B17" t="s">
-        <v>110</v>
+        <v>222</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>112</v>
+        <v>221</v>
       </c>
       <c r="H17">
         <v>12</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="K17" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>115</v>
       </c>
@@ -1697,8 +1758,11 @@
       <c r="H18">
         <v>12</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="K18" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>130</v>
       </c>
@@ -1717,8 +1781,11 @@
       <c r="H19">
         <v>12</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="K19" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>143</v>
       </c>
@@ -1737,8 +1804,11 @@
       <c r="H20">
         <v>12</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="K20" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>194</v>
       </c>
@@ -1754,8 +1824,11 @@
       <c r="H21">
         <v>12</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="K21" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>190</v>
       </c>
@@ -1774,8 +1847,11 @@
       <c r="H22">
         <v>12</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="K22" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>209</v>
       </c>
@@ -1794,8 +1870,11 @@
       <c r="H23">
         <v>12</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="K23" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>195</v>
       </c>
@@ -1814,8 +1893,11 @@
       <c r="H24">
         <v>12</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="K24" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>201</v>
       </c>
@@ -1834,13 +1916,16 @@
       <c r="H25">
         <v>12</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="K25" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>271</v>
+      </c>
+      <c r="B26" t="s">
         <v>272</v>
-      </c>
-      <c r="B26" t="s">
-        <v>273</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>28</v>
@@ -1849,10 +1934,13 @@
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H26">
         <v>12</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -1863,7 +1951,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2B8FC54-75D4-4AC2-B92C-338AB72929A6}">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.83203125" bestFit="1" customWidth="1"/>
@@ -2020,23 +2108,23 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>183</v>
@@ -2044,23 +2132,23 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>183</v>
@@ -2068,13 +2156,13 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>59</v>
@@ -2084,7 +2172,7 @@
       </c>
       <c r="F9" s="1"/>
       <c r="G9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>183</v>
@@ -2101,7 +2189,7 @@
         <v>41</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -2158,10 +2246,10 @@
         <v>62</v>
       </c>
       <c r="B13" t="s">
+        <v>297</v>
+      </c>
+      <c r="C13" t="s">
         <v>270</v>
-      </c>
-      <c r="C13" t="s">
-        <v>271</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>6</v>
@@ -2184,7 +2272,7 @@
         <v>84</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -2218,22 +2306,19 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>269</v>
+        <v>62</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>294</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>295</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="E16">
         <v>1</v>
-      </c>
-      <c r="G16" t="s">
-        <v>93</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>183</v>
@@ -2244,16 +2329,19 @@
         <v>269</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E17">
         <v>1</v>
+      </c>
+      <c r="G17" t="s">
+        <v>93</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>183</v>
@@ -2264,10 +2352,10 @@
         <v>269</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>56</v>
@@ -2284,10 +2372,10 @@
         <v>269</v>
       </c>
       <c r="B19" t="s">
-        <v>237</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>264</v>
+        <v>101</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>56</v>
@@ -2304,10 +2392,10 @@
         <v>269</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>237</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>264</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>56</v>
@@ -2321,97 +2409,99 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="B21" t="s">
-        <v>170</v>
+        <v>107</v>
       </c>
       <c r="C21" t="s">
-        <v>173</v>
+        <v>108</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
-      <c r="F21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>221</v>
+        <v>112</v>
       </c>
       <c r="B22" t="s">
-        <v>171</v>
+        <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>172</v>
+        <v>114</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>27</v>
+        <v>293</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
-      <c r="F22" s="1"/>
+      <c r="G22" t="s">
+        <v>113</v>
+      </c>
       <c r="H22" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>221</v>
+        <v>112</v>
       </c>
       <c r="B23" t="s">
-        <v>174</v>
+        <v>274</v>
       </c>
       <c r="C23" t="s">
-        <v>176</v>
+        <v>275</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>27</v>
+        <v>293</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
-      <c r="F23" s="1"/>
+      <c r="G23" t="s">
+        <v>276</v>
+      </c>
       <c r="H23" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>221</v>
+        <v>112</v>
       </c>
       <c r="B24" t="s">
-        <v>175</v>
+        <v>297</v>
       </c>
       <c r="C24" t="s">
-        <v>177</v>
+        <v>270</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>27</v>
+        <v>293</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
-      <c r="F24" s="1"/>
       <c r="H24" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>221</v>
+        <v>112</v>
       </c>
       <c r="B25" t="s">
-        <v>180</v>
+        <v>216</v>
       </c>
       <c r="C25" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>27</v>
@@ -2419,30 +2509,34 @@
       <c r="E25">
         <v>1</v>
       </c>
-      <c r="F25" s="1"/>
+      <c r="F25">
+        <v>0</v>
+      </c>
       <c r="H25" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>221</v>
+        <v>112</v>
       </c>
       <c r="B26" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C26" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="E26">
-        <v>1</v>
-      </c>
-      <c r="F26" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
       <c r="H26" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -2450,21 +2544,18 @@
         <v>221</v>
       </c>
       <c r="B27" t="s">
-        <v>244</v>
+        <v>170</v>
       </c>
       <c r="C27" t="s">
-        <v>245</v>
+        <v>173</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27" s="1"/>
-      <c r="G27" t="s">
-        <v>50</v>
-      </c>
       <c r="H27" s="1" t="s">
         <v>182</v>
       </c>
@@ -2474,21 +2565,18 @@
         <v>221</v>
       </c>
       <c r="B28" t="s">
-        <v>246</v>
+        <v>171</v>
       </c>
       <c r="C28" t="s">
-        <v>247</v>
+        <v>172</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
       <c r="F28" s="1"/>
-      <c r="G28" t="s">
-        <v>248</v>
-      </c>
       <c r="H28" s="1" t="s">
         <v>182</v>
       </c>
@@ -2498,21 +2586,18 @@
         <v>221</v>
       </c>
       <c r="B29" t="s">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="C29" t="s">
-        <v>230</v>
+        <v>176</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29" s="1"/>
-      <c r="G29" t="s">
-        <v>226</v>
-      </c>
       <c r="H29" s="1" t="s">
         <v>182</v>
       </c>
@@ -2522,13 +2607,13 @@
         <v>221</v>
       </c>
       <c r="B30" t="s">
-        <v>229</v>
+        <v>175</v>
       </c>
       <c r="C30" t="s">
-        <v>231</v>
+        <v>177</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -2543,13 +2628,13 @@
         <v>221</v>
       </c>
       <c r="B31" t="s">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="C31" t="s">
-        <v>233</v>
+        <v>181</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -2564,21 +2649,18 @@
         <v>221</v>
       </c>
       <c r="B32" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="C32" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
       <c r="F32" s="1"/>
-      <c r="G32" t="s">
-        <v>50</v>
-      </c>
       <c r="H32" s="1" t="s">
         <v>182</v>
       </c>
@@ -2588,18 +2670,21 @@
         <v>221</v>
       </c>
       <c r="B33" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="C33" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33" s="1"/>
+      <c r="G33" t="s">
+        <v>50</v>
+      </c>
       <c r="H33" s="1" t="s">
         <v>182</v>
       </c>
@@ -2609,18 +2694,21 @@
         <v>221</v>
       </c>
       <c r="B34" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C34" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="E34">
         <v>1</v>
       </c>
       <c r="F34" s="1"/>
+      <c r="G34" t="s">
+        <v>248</v>
+      </c>
       <c r="H34" s="1" t="s">
         <v>182</v>
       </c>
@@ -2630,20 +2718,20 @@
         <v>221</v>
       </c>
       <c r="B35" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="C35" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" t="s">
-        <v>50</v>
+        <v>226</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>182</v>
@@ -2654,175 +2742,175 @@
         <v>221</v>
       </c>
       <c r="B36" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="C36" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="E36">
         <v>1</v>
       </c>
       <c r="F36" s="1"/>
-      <c r="G36" t="s">
-        <v>50</v>
-      </c>
       <c r="H36" s="1" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>112</v>
+        <v>221</v>
       </c>
       <c r="B37" t="s">
-        <v>109</v>
+        <v>232</v>
       </c>
       <c r="C37" t="s">
-        <v>114</v>
+        <v>233</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>294</v>
+        <v>56</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
-      <c r="G37" t="s">
-        <v>113</v>
-      </c>
+      <c r="F37" s="1"/>
       <c r="H37" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>112</v>
+        <v>221</v>
       </c>
       <c r="B38" t="s">
-        <v>216</v>
+        <v>243</v>
       </c>
       <c r="C38" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
-      <c r="F38">
-        <v>0</v>
+      <c r="F38" s="1"/>
+      <c r="G38" t="s">
+        <v>50</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>112</v>
+        <v>221</v>
       </c>
       <c r="B39" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="C39" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E39">
-        <v>0</v>
-      </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F39" s="1"/>
       <c r="H39" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>117</v>
+        <v>221</v>
       </c>
       <c r="B40" t="s">
-        <v>134</v>
+        <v>237</v>
       </c>
       <c r="C40" t="s">
-        <v>118</v>
+        <v>238</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>294</v>
+        <v>56</v>
       </c>
       <c r="E40">
         <v>1</v>
       </c>
-      <c r="G40" t="s">
-        <v>119</v>
-      </c>
+      <c r="F40" s="1"/>
       <c r="H40" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>117</v>
+        <v>221</v>
       </c>
       <c r="B41" t="s">
-        <v>135</v>
+        <v>239</v>
       </c>
       <c r="C41" t="s">
-        <v>125</v>
+        <v>241</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="E41">
         <v>1</v>
       </c>
+      <c r="F41" s="1"/>
       <c r="G41" t="s">
-        <v>126</v>
+        <v>50</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>117</v>
+        <v>221</v>
       </c>
       <c r="B42" t="s">
-        <v>265</v>
+        <v>240</v>
       </c>
       <c r="C42" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
+      <c r="F42" s="1"/>
+      <c r="G42" t="s">
+        <v>50</v>
+      </c>
       <c r="H42" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="B43" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C43" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>56</v>
+        <v>293</v>
       </c>
       <c r="E43">
         <v>1</v>
+      </c>
+      <c r="G43" t="s">
+        <v>119</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>183</v>
@@ -2830,19 +2918,22 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="B44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C44" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="E44">
         <v>1</v>
+      </c>
+      <c r="G44" t="s">
+        <v>126</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>183</v>
@@ -2850,13 +2941,13 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="B45" t="s">
-        <v>141</v>
+        <v>265</v>
       </c>
       <c r="C45" t="s">
-        <v>138</v>
+        <v>266</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>56</v>
@@ -2873,10 +2964,10 @@
         <v>132</v>
       </c>
       <c r="B46" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C46" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>56</v>
@@ -2890,22 +2981,19 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="B47" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C47" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E47">
         <v>1</v>
-      </c>
-      <c r="G47" t="s">
-        <v>50</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>183</v>
@@ -2913,22 +3001,19 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="B48" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C48" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="E48">
         <v>1</v>
-      </c>
-      <c r="G48" t="s">
-        <v>50</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>183</v>
@@ -2936,22 +3021,19 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="B49" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="C49" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E49">
         <v>1</v>
-      </c>
-      <c r="G49" t="s">
-        <v>153</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>183</v>
@@ -2962,16 +3044,19 @@
         <v>145</v>
       </c>
       <c r="B50" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C50" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="E50">
         <v>1</v>
+      </c>
+      <c r="G50" t="s">
+        <v>50</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>183</v>
@@ -2979,19 +3064,22 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>211</v>
+        <v>145</v>
       </c>
       <c r="B51" t="s">
-        <v>212</v>
+        <v>147</v>
       </c>
       <c r="C51" t="s">
-        <v>213</v>
+        <v>149</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="E51">
         <v>1</v>
+      </c>
+      <c r="G51" t="s">
+        <v>50</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>183</v>
@@ -2999,19 +3087,22 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>211</v>
+        <v>145</v>
       </c>
       <c r="B52" t="s">
-        <v>214</v>
+        <v>159</v>
       </c>
       <c r="C52" t="s">
-        <v>215</v>
+        <v>150</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E52">
         <v>1</v>
+      </c>
+      <c r="G52" t="s">
+        <v>153</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>183</v>
@@ -3019,22 +3110,19 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>196</v>
+        <v>145</v>
       </c>
       <c r="B53" t="s">
-        <v>198</v>
+        <v>151</v>
       </c>
       <c r="C53" t="s">
-        <v>199</v>
+        <v>152</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>294</v>
+        <v>56</v>
       </c>
       <c r="E53">
         <v>1</v>
-      </c>
-      <c r="G53" t="s">
-        <v>113</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>183</v>
@@ -3042,16 +3130,16 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B54" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="C54" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E54">
         <v>1</v>
@@ -3062,16 +3150,16 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B55" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="C55" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="E55">
         <v>1</v>
@@ -3082,16 +3170,16 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B56" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C56" t="s">
         <v>199</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E56">
         <v>1</v>
@@ -3105,10 +3193,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B57" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C57" t="s">
         <v>208</v>
@@ -3125,10 +3213,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B58" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C58" t="s">
         <v>179</v>
@@ -3145,16 +3233,16 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>274</v>
+        <v>204</v>
       </c>
       <c r="B59" t="s">
-        <v>109</v>
+        <v>206</v>
       </c>
       <c r="C59" t="s">
-        <v>114</v>
+        <v>199</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E59">
         <v>1</v>
@@ -3168,22 +3256,19 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>274</v>
+        <v>204</v>
       </c>
       <c r="B60" t="s">
-        <v>275</v>
+        <v>205</v>
       </c>
       <c r="C60" t="s">
-        <v>276</v>
+        <v>208</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>294</v>
+        <v>27</v>
       </c>
       <c r="E60">
         <v>1</v>
-      </c>
-      <c r="G60" t="s">
-        <v>277</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>183</v>
@@ -3191,10 +3276,10 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>274</v>
+        <v>204</v>
       </c>
       <c r="B61" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="C61" t="s">
         <v>179</v>
@@ -3206,6 +3291,72 @@
         <v>1</v>
       </c>
       <c r="H61" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>273</v>
+      </c>
+      <c r="B62" t="s">
+        <v>109</v>
+      </c>
+      <c r="C62" t="s">
+        <v>114</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="G62" t="s">
+        <v>113</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>273</v>
+      </c>
+      <c r="B63" t="s">
+        <v>274</v>
+      </c>
+      <c r="C63" t="s">
+        <v>275</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="G63" t="s">
+        <v>276</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>273</v>
+      </c>
+      <c r="B64" t="s">
+        <v>280</v>
+      </c>
+      <c r="C64" t="s">
+        <v>179</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+      <c r="H64" s="1" t="s">
         <v>183</v>
       </c>
     </row>
@@ -3217,7 +3368,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{256469AD-8C25-494B-B7FC-7D7B2DDE1DC0}">
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -3887,24 +4038,35 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
+        <v>277</v>
+      </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61" t="s">
         <v>278</v>
-      </c>
-      <c r="B61">
-        <v>1</v>
-      </c>
-      <c r="C61" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B62">
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>280</v>
+        <v>279</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>277</v>
+      </c>
+      <c r="B63">
+        <v>3</v>
+      </c>
+      <c r="C63" t="s">
+        <v>296</v>
       </c>
     </row>
   </sheetData>

--- a/backend/storage/schema/quotation_template.xlsx
+++ b/backend/storage/schema/quotation_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/longlh123/Languages/GitHub/IPSOS-FINANCE-PAYMENT/backend/storage/schema/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C82794-2C6F-AC46-851E-F0BE86B4F9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C91926-6C16-9B43-B318-2472916B500B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6260" yWindow="3100" windowWidth="29040" windowHeight="17520" xr2:uid="{C9138D76-07EC-41C4-8817-AFCBF30C50C2}"/>
+    <workbookView xWindow="5740" yWindow="3680" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{C9138D76-07EC-41C4-8817-AFCBF30C50C2}"/>
   </bookViews>
   <sheets>
     <sheet name="FIELDS" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="323">
   <si>
     <t>field_name</t>
   </si>
@@ -64,24 +64,12 @@
     <t>iquote_link</t>
   </si>
   <si>
-    <t>Link iQuote</t>
-  </si>
-  <si>
     <t>pitch_number</t>
   </si>
   <si>
-    <t>Số Pitch</t>
-  </si>
-  <si>
-    <t>Project No. (Internal number)</t>
-  </si>
-  <si>
     <t>client_name</t>
   </si>
   <si>
-    <t xml:space="preserve">Tên Dự án </t>
-  </si>
-  <si>
     <t>Tên Khách hàng (*)</t>
   </si>
   <si>
@@ -211,9 +199,6 @@
     <t>textarea</t>
   </si>
   <si>
-    <t>Platform</t>
-  </si>
-  <si>
     <t>internal_code</t>
   </si>
   <si>
@@ -535,9 +520,6 @@
     <t>excel:research_type</t>
   </si>
   <si>
-    <t>Sản phẩm nghiên cứu</t>
-  </si>
-  <si>
     <t>Product Test - Monadic</t>
   </si>
   <si>
@@ -886,9 +868,6 @@
     <t>Phương pháp nghiên cứu</t>
   </si>
   <si>
-    <t>product_classification</t>
-  </si>
-  <si>
     <t>industry</t>
   </si>
   <si>
@@ -907,9 +886,6 @@
     <t>Loại sản phẩm</t>
   </si>
   <si>
-    <t>product_classification_config</t>
-  </si>
-  <si>
     <t>db:industries</t>
   </si>
   <si>
@@ -932,6 +908,105 @@
   </si>
   <si>
     <t>target_audience</t>
+  </si>
+  <si>
+    <t>Link iQuote (*)</t>
+  </si>
+  <si>
+    <t>Số Pitch (*)</t>
+  </si>
+  <si>
+    <t>Project No. (Internal number) (*)</t>
+  </si>
+  <si>
+    <t>Tên Dự án (*)</t>
+  </si>
+  <si>
+    <t>project_information</t>
+  </si>
+  <si>
+    <t>Thông tin dự án</t>
+  </si>
+  <si>
+    <t>project_information_config</t>
+  </si>
+  <si>
+    <t>placeholder</t>
+  </si>
+  <si>
+    <t>https://nwb.ipsos.com/iquote/#...</t>
+  </si>
+  <si>
+    <t>VD: 26060001</t>
+  </si>
+  <si>
+    <t>VD: 2026-061</t>
+  </si>
+  <si>
+    <t>Tên ngắn gọn</t>
+  </si>
+  <si>
+    <t>Tên công ty KH</t>
+  </si>
+  <si>
+    <t>excel:bu_research_teams</t>
+  </si>
+  <si>
+    <t>bu_research_teams</t>
+  </si>
+  <si>
+    <t>550101 – BHT VN</t>
+  </si>
+  <si>
+    <t>50102 – CHP</t>
+  </si>
+  <si>
+    <t>550103 – INNO</t>
+  </si>
+  <si>
+    <t>550104 – HEC</t>
+  </si>
+  <si>
+    <t>550106 – CEX</t>
+  </si>
+  <si>
+    <t>550107 – S3</t>
+  </si>
+  <si>
+    <t>550103 – MSU</t>
+  </si>
+  <si>
+    <t>--- Vui lòng chọn ---</t>
+  </si>
+  <si>
+    <t>target_group</t>
+  </si>
+  <si>
+    <t>Mục tiêu</t>
+  </si>
+  <si>
+    <t>target_group_config</t>
+  </si>
+  <si>
+    <t>Mô tả mục tiêu nghiên cứu...</t>
+  </si>
+  <si>
+    <t>clt_count</t>
+  </si>
+  <si>
+    <t>Số lần lên CLT</t>
+  </si>
+  <si>
+    <t>VD: 1</t>
+  </si>
+  <si>
+    <t>Phần mềm / Nền tảng</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>Quota sampling</t>
   </si>
 </sst>
 </file>
@@ -980,12 +1055,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1320,7 +1396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6694FA44-4A7D-4629-A892-7DFDEEB80386}">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -1347,600 +1423,414 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>294</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>295</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="D2">
         <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>296</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2">
         <v>12</v>
       </c>
-      <c r="I2">
-        <v>6</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>313</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>314</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="D3">
         <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>315</v>
       </c>
       <c r="H3">
         <v>12</v>
       </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>155</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>275</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0</v>
-      </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+        <v>77</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>156</v>
+      </c>
       <c r="H4">
         <v>12</v>
       </c>
-      <c r="I4">
-        <v>6</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="1">
-        <v>0</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>74</v>
+      </c>
       <c r="H5">
         <v>12</v>
       </c>
-      <c r="I5">
-        <v>6</v>
-      </c>
       <c r="K5" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>57</v>
       </c>
       <c r="H6">
         <v>12</v>
       </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
       <c r="K6" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>261</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>262</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="D7">
         <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>263</v>
       </c>
       <c r="H7">
         <v>12</v>
       </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
       <c r="K7" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>293</v>
+        <v>24</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
-      <c r="G8" t="s">
-        <v>66</v>
+      <c r="F8" t="s">
+        <v>107</v>
       </c>
       <c r="H8">
         <v>12</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>215</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>216</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="D9">
         <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>215</v>
       </c>
       <c r="H9">
         <v>12</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
-      <c r="G10" t="s">
-        <v>65</v>
+      <c r="F10" t="s">
+        <v>112</v>
       </c>
       <c r="H10">
         <v>12</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="B11" t="s">
-        <v>281</v>
+        <v>126</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>161</v>
+      <c r="F11" t="s">
+        <v>127</v>
       </c>
       <c r="H11">
         <v>12</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>282</v>
+        <v>138</v>
       </c>
       <c r="B12" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>289</v>
+        <v>140</v>
       </c>
       <c r="H12">
         <v>12</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>77</v>
+        <v>188</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>187</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D13">
         <v>1</v>
-      </c>
-      <c r="F13" t="s">
-        <v>79</v>
       </c>
       <c r="H13">
         <v>12</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>184</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>185</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
-      <c r="F14" t="s">
-        <v>62</v>
+      <c r="G14" t="s">
+        <v>186</v>
       </c>
       <c r="H14">
         <v>12</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>267</v>
+        <v>203</v>
       </c>
       <c r="B15" t="s">
-        <v>268</v>
+        <v>204</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>269</v>
+        <v>205</v>
       </c>
       <c r="H15">
         <v>12</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>111</v>
+        <v>189</v>
       </c>
       <c r="B16" t="s">
-        <v>110</v>
+        <v>197</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>112</v>
+        <v>190</v>
       </c>
       <c r="H16">
         <v>12</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="H17">
         <v>12</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>115</v>
+        <v>265</v>
       </c>
       <c r="B18" t="s">
-        <v>116</v>
+        <v>266</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>117</v>
+        <v>267</v>
       </c>
       <c r="H18">
         <v>12</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>130</v>
-      </c>
-      <c r="B19" t="s">
-        <v>131</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="F19" t="s">
-        <v>132</v>
-      </c>
-      <c r="H19">
-        <v>12</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>143</v>
-      </c>
-      <c r="B20" t="s">
-        <v>144</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="F20" t="s">
-        <v>145</v>
-      </c>
-      <c r="H20">
-        <v>12</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>194</v>
-      </c>
-      <c r="B21" t="s">
-        <v>193</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="H21">
-        <v>12</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>190</v>
-      </c>
-      <c r="B22" t="s">
-        <v>191</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="G22" t="s">
-        <v>192</v>
-      </c>
-      <c r="H22">
-        <v>12</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>209</v>
-      </c>
-      <c r="B23" t="s">
-        <v>210</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="F23" t="s">
-        <v>211</v>
-      </c>
-      <c r="H23">
-        <v>12</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>195</v>
-      </c>
-      <c r="B24" t="s">
-        <v>203</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-      <c r="F24" t="s">
-        <v>196</v>
-      </c>
-      <c r="H24">
-        <v>12</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>201</v>
-      </c>
-      <c r="B25" t="s">
-        <v>202</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-      <c r="F25" t="s">
-        <v>204</v>
-      </c>
-      <c r="H25">
-        <v>12</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>271</v>
-      </c>
-      <c r="B26" t="s">
-        <v>272</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-      <c r="F26" t="s">
-        <v>273</v>
-      </c>
-      <c r="H26">
-        <v>12</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -1951,21 +1841,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2B8FC54-75D4-4AC2-B92C-338AB72929A6}">
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.5" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1974,1390 +1865,1660 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>291</v>
+      </c>
+      <c r="D3" t="s">
+        <v>299</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>296</v>
+      </c>
+      <c r="B4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" t="s">
+        <v>292</v>
+      </c>
+      <c r="D4" t="s">
+        <v>300</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>296</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>293</v>
+      </c>
+      <c r="D5" t="s">
+        <v>301</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>296</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>302</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>296</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>315</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>316</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>315</v>
+      </c>
+      <c r="B9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" t="s">
+        <v>279</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" t="s">
+        <v>282</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>315</v>
+      </c>
+      <c r="B10" t="s">
+        <v>277</v>
+      </c>
+      <c r="C10" t="s">
+        <v>280</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" t="s">
+        <v>283</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>315</v>
+      </c>
+      <c r="B11" t="s">
+        <v>278</v>
+      </c>
+      <c r="C11" t="s">
+        <v>281</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" t="s">
+        <v>284</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="H12" t="s">
+        <v>61</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B13" t="s">
+        <v>317</v>
+      </c>
+      <c r="C13" t="s">
+        <v>318</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" t="s">
+        <v>62</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>320</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="H15" t="s">
+        <v>60</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B16" t="s">
+        <v>178</v>
+      </c>
+      <c r="C16" t="s">
+        <v>179</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" t="s">
+        <v>180</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" t="s">
+        <v>71</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B18" t="s">
+        <v>172</v>
+      </c>
+      <c r="C18" t="s">
+        <v>173</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="I18" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B19" t="s">
+        <v>158</v>
+      </c>
+      <c r="C19" t="s">
+        <v>157</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" t="s">
+        <v>159</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B20" t="s">
         <v>75</v>
       </c>
-      <c r="C2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B3" t="s">
-        <v>184</v>
-      </c>
-      <c r="C3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" t="s">
-        <v>186</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B4" t="s">
-        <v>163</v>
-      </c>
-      <c r="C4" t="s">
-        <v>162</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" t="s">
+      <c r="C20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="H20" t="s">
+        <v>76</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" t="s">
+        <v>99</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
+        <v>100</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" t="s">
+        <v>289</v>
+      </c>
+      <c r="C23" t="s">
+        <v>264</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="H24" t="s">
+        <v>80</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" t="s">
+        <v>85</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" t="s">
+        <v>286</v>
+      </c>
+      <c r="C26" t="s">
+        <v>287</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>263</v>
+      </c>
+      <c r="B27" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" t="s">
+        <v>87</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="H27" t="s">
+        <v>88</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>263</v>
+      </c>
+      <c r="B28" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>263</v>
+      </c>
+      <c r="B29" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>263</v>
+      </c>
+      <c r="B30" t="s">
+        <v>231</v>
+      </c>
+      <c r="C30" t="s">
+        <v>258</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>263</v>
+      </c>
+      <c r="B31" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" t="s">
+        <v>103</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" t="s">
+        <v>104</v>
+      </c>
+      <c r="C32" t="s">
+        <v>109</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="H32" t="s">
+        <v>108</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>107</v>
+      </c>
+      <c r="B33" t="s">
+        <v>268</v>
+      </c>
+      <c r="C33" t="s">
+        <v>269</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="H33" t="s">
+        <v>270</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>107</v>
+      </c>
+      <c r="B34" t="s">
+        <v>289</v>
+      </c>
+      <c r="C34" t="s">
+        <v>264</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>107</v>
+      </c>
+      <c r="B35" t="s">
+        <v>210</v>
+      </c>
+      <c r="C35" t="s">
+        <v>212</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" t="s">
+        <v>211</v>
+      </c>
+      <c r="C36" t="s">
+        <v>213</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>215</v>
+      </c>
+      <c r="B37" t="s">
         <v>164</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" t="s">
-        <v>76</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B6" t="s">
-        <v>178</v>
-      </c>
-      <c r="C6" t="s">
-        <v>179</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="H6" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>289</v>
-      </c>
-      <c r="B7" t="s">
-        <v>283</v>
-      </c>
-      <c r="C7" t="s">
-        <v>286</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" t="s">
-        <v>290</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>289</v>
-      </c>
-      <c r="B8" t="s">
-        <v>284</v>
-      </c>
-      <c r="C8" t="s">
-        <v>287</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" t="s">
-        <v>291</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>289</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C37" t="s">
+        <v>167</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37" s="1"/>
+      <c r="I37" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>215</v>
+      </c>
+      <c r="B38" t="s">
+        <v>165</v>
+      </c>
+      <c r="C38" t="s">
+        <v>166</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38" s="1"/>
+      <c r="I38" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>215</v>
+      </c>
+      <c r="B39" t="s">
+        <v>168</v>
+      </c>
+      <c r="C39" t="s">
+        <v>170</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39" s="1"/>
+      <c r="I39" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>215</v>
+      </c>
+      <c r="B40" t="s">
+        <v>169</v>
+      </c>
+      <c r="C40" t="s">
+        <v>171</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40" s="1"/>
+      <c r="I40" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>215</v>
+      </c>
+      <c r="B41" t="s">
+        <v>174</v>
+      </c>
+      <c r="C41" t="s">
+        <v>175</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1"/>
+      <c r="I41" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>215</v>
+      </c>
+      <c r="B42" t="s">
+        <v>217</v>
+      </c>
+      <c r="C42" t="s">
+        <v>218</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42" s="1"/>
+      <c r="I42" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>215</v>
+      </c>
+      <c r="B43" t="s">
+        <v>238</v>
+      </c>
+      <c r="C43" t="s">
+        <v>239</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43" s="1"/>
+      <c r="H43" t="s">
+        <v>46</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>215</v>
+      </c>
+      <c r="B44" t="s">
+        <v>240</v>
+      </c>
+      <c r="C44" t="s">
+        <v>241</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1"/>
+      <c r="H44" t="s">
+        <v>242</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>215</v>
+      </c>
+      <c r="B45" t="s">
+        <v>219</v>
+      </c>
+      <c r="C45" t="s">
+        <v>224</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45" s="1"/>
+      <c r="H45" t="s">
+        <v>220</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>215</v>
+      </c>
+      <c r="B46" t="s">
+        <v>223</v>
+      </c>
+      <c r="C46" t="s">
+        <v>225</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46" s="1"/>
+      <c r="I46" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>215</v>
+      </c>
+      <c r="B47" t="s">
+        <v>226</v>
+      </c>
+      <c r="C47" t="s">
+        <v>227</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47" s="1"/>
+      <c r="I47" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>215</v>
+      </c>
+      <c r="B48" t="s">
+        <v>237</v>
+      </c>
+      <c r="C48" t="s">
+        <v>229</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48" s="1"/>
+      <c r="H48" t="s">
+        <v>46</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>215</v>
+      </c>
+      <c r="B49" t="s">
+        <v>230</v>
+      </c>
+      <c r="C49" t="s">
+        <v>228</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49" s="1"/>
+      <c r="I49" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>215</v>
+      </c>
+      <c r="B50" t="s">
+        <v>231</v>
+      </c>
+      <c r="C50" t="s">
+        <v>232</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50" s="1"/>
+      <c r="I50" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>215</v>
+      </c>
+      <c r="B51" t="s">
+        <v>233</v>
+      </c>
+      <c r="C51" t="s">
+        <v>235</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51" s="1"/>
+      <c r="H51" t="s">
+        <v>46</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>215</v>
+      </c>
+      <c r="B52" t="s">
+        <v>234</v>
+      </c>
+      <c r="C52" t="s">
+        <v>236</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52" s="1"/>
+      <c r="H52" t="s">
+        <v>46</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>112</v>
+      </c>
+      <c r="B53" t="s">
+        <v>129</v>
+      </c>
+      <c r="C53" t="s">
+        <v>113</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C9" t="s">
-        <v>288</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" t="s">
-        <v>292</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>79</v>
-      </c>
-      <c r="B10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>81</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="H53" t="s">
+        <v>114</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>112</v>
+      </c>
+      <c r="B54" t="s">
+        <v>130</v>
+      </c>
+      <c r="C54" t="s">
+        <v>120</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="H54" t="s">
+        <v>121</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>112</v>
+      </c>
+      <c r="B55" t="s">
+        <v>259</v>
+      </c>
+      <c r="C55" t="s">
+        <v>260</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>127</v>
+      </c>
+      <c r="B56" t="s">
+        <v>135</v>
+      </c>
+      <c r="C56" t="s">
+        <v>128</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>127</v>
+      </c>
+      <c r="B57" t="s">
+        <v>131</v>
+      </c>
+      <c r="C57" t="s">
+        <v>132</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>127</v>
+      </c>
+      <c r="B58" t="s">
+        <v>136</v>
+      </c>
+      <c r="C58" t="s">
+        <v>133</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>127</v>
+      </c>
+      <c r="B59" t="s">
+        <v>137</v>
+      </c>
+      <c r="C59" t="s">
+        <v>134</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>140</v>
+      </c>
+      <c r="B60" t="s">
+        <v>141</v>
+      </c>
+      <c r="C60" t="s">
+        <v>143</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="H60" t="s">
+        <v>46</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>140</v>
+      </c>
+      <c r="B61" t="s">
+        <v>142</v>
+      </c>
+      <c r="C61" t="s">
+        <v>144</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="H61" t="s">
+        <v>46</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>140</v>
+      </c>
+      <c r="B62" t="s">
+        <v>154</v>
+      </c>
+      <c r="C62" t="s">
+        <v>145</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="H62" t="s">
+        <v>148</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>140</v>
+      </c>
+      <c r="B63" t="s">
+        <v>146</v>
+      </c>
+      <c r="C63" t="s">
+        <v>147</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>205</v>
+      </c>
+      <c r="B64" t="s">
+        <v>206</v>
+      </c>
+      <c r="C64" t="s">
+        <v>207</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>205</v>
+      </c>
+      <c r="B65" t="s">
+        <v>208</v>
+      </c>
+      <c r="C65" t="s">
+        <v>209</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>190</v>
+      </c>
+      <c r="B66" t="s">
+        <v>192</v>
+      </c>
+      <c r="C66" t="s">
+        <v>193</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="H66" t="s">
+        <v>108</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>190</v>
+      </c>
+      <c r="B67" t="s">
+        <v>191</v>
+      </c>
+      <c r="C67" t="s">
+        <v>202</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>190</v>
+      </c>
+      <c r="B68" t="s">
+        <v>194</v>
+      </c>
+      <c r="C68" t="s">
+        <v>173</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>198</v>
+      </c>
+      <c r="B69" t="s">
+        <v>200</v>
+      </c>
+      <c r="C69" t="s">
+        <v>193</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F69">
+        <v>1</v>
+      </c>
+      <c r="H69" t="s">
+        <v>108</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>198</v>
+      </c>
+      <c r="B70" t="s">
+        <v>199</v>
+      </c>
+      <c r="C70" t="s">
+        <v>202</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>198</v>
+      </c>
+      <c r="B71" t="s">
+        <v>201</v>
+      </c>
+      <c r="C71" t="s">
+        <v>173</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>267</v>
+      </c>
+      <c r="B72" t="s">
         <v>104</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>79</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="s">
-        <v>105</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" t="s">
-        <v>297</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="C72" t="s">
+        <v>109</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="H72" t="s">
+        <v>108</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>267</v>
+      </c>
+      <c r="B73" t="s">
+        <v>268</v>
+      </c>
+      <c r="C73" t="s">
+        <v>269</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="H73" t="s">
         <v>270</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="I73" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>267</v>
+      </c>
+      <c r="B74" t="s">
+        <v>274</v>
+      </c>
+      <c r="C74" t="s">
+        <v>173</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="G14" t="s">
-        <v>85</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>62</v>
-      </c>
-      <c r="B16" t="s">
-        <v>294</v>
-      </c>
-      <c r="C16" t="s">
-        <v>295</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>269</v>
-      </c>
-      <c r="B17" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" t="s">
-        <v>92</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="G17" t="s">
-        <v>93</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>269</v>
-      </c>
-      <c r="B18" t="s">
-        <v>102</v>
-      </c>
-      <c r="C18" t="s">
-        <v>103</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>269</v>
-      </c>
-      <c r="B19" t="s">
-        <v>100</v>
-      </c>
-      <c r="C19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>269</v>
-      </c>
-      <c r="B20" t="s">
-        <v>237</v>
-      </c>
-      <c r="C20" t="s">
-        <v>264</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20">
-        <v>1</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>269</v>
-      </c>
-      <c r="B21" t="s">
-        <v>107</v>
-      </c>
-      <c r="C21" t="s">
-        <v>108</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E21">
-        <v>1</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>112</v>
-      </c>
-      <c r="B22" t="s">
-        <v>109</v>
-      </c>
-      <c r="C22" t="s">
-        <v>114</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="G22" t="s">
-        <v>113</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>112</v>
-      </c>
-      <c r="B23" t="s">
-        <v>274</v>
-      </c>
-      <c r="C23" t="s">
-        <v>275</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="G23" t="s">
-        <v>276</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>112</v>
-      </c>
-      <c r="B24" t="s">
-        <v>297</v>
-      </c>
-      <c r="C24" t="s">
-        <v>270</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>112</v>
-      </c>
-      <c r="B25" t="s">
-        <v>216</v>
-      </c>
-      <c r="C25" t="s">
-        <v>218</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>112</v>
-      </c>
-      <c r="B26" t="s">
-        <v>217</v>
-      </c>
-      <c r="C26" t="s">
-        <v>219</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>221</v>
-      </c>
-      <c r="B27" t="s">
-        <v>170</v>
-      </c>
-      <c r="C27" t="s">
-        <v>173</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E27">
-        <v>1</v>
-      </c>
-      <c r="F27" s="1"/>
-      <c r="H27" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>221</v>
-      </c>
-      <c r="B28" t="s">
-        <v>171</v>
-      </c>
-      <c r="C28" t="s">
-        <v>172</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E28">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1"/>
-      <c r="H28" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>221</v>
-      </c>
-      <c r="B29" t="s">
-        <v>174</v>
-      </c>
-      <c r="C29" t="s">
-        <v>176</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-      <c r="F29" s="1"/>
-      <c r="H29" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>221</v>
-      </c>
-      <c r="B30" t="s">
-        <v>175</v>
-      </c>
-      <c r="C30" t="s">
-        <v>177</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E30">
-        <v>1</v>
-      </c>
-      <c r="F30" s="1"/>
-      <c r="H30" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>221</v>
-      </c>
-      <c r="B31" t="s">
-        <v>180</v>
-      </c>
-      <c r="C31" t="s">
-        <v>181</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E31">
-        <v>1</v>
-      </c>
-      <c r="F31" s="1"/>
-      <c r="H31" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>221</v>
-      </c>
-      <c r="B32" t="s">
-        <v>223</v>
-      </c>
-      <c r="C32" t="s">
-        <v>224</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E32">
-        <v>1</v>
-      </c>
-      <c r="F32" s="1"/>
-      <c r="H32" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>221</v>
-      </c>
-      <c r="B33" t="s">
-        <v>244</v>
-      </c>
-      <c r="C33" t="s">
-        <v>245</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E33">
-        <v>1</v>
-      </c>
-      <c r="F33" s="1"/>
-      <c r="G33" t="s">
-        <v>50</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>221</v>
-      </c>
-      <c r="B34" t="s">
-        <v>246</v>
-      </c>
-      <c r="C34" t="s">
-        <v>247</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E34">
-        <v>1</v>
-      </c>
-      <c r="F34" s="1"/>
-      <c r="G34" t="s">
-        <v>248</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>221</v>
-      </c>
-      <c r="B35" t="s">
-        <v>225</v>
-      </c>
-      <c r="C35" t="s">
-        <v>230</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E35">
-        <v>1</v>
-      </c>
-      <c r="F35" s="1"/>
-      <c r="G35" t="s">
-        <v>226</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>221</v>
-      </c>
-      <c r="B36" t="s">
-        <v>229</v>
-      </c>
-      <c r="C36" t="s">
-        <v>231</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E36">
-        <v>1</v>
-      </c>
-      <c r="F36" s="1"/>
-      <c r="H36" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>221</v>
-      </c>
-      <c r="B37" t="s">
-        <v>232</v>
-      </c>
-      <c r="C37" t="s">
-        <v>233</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E37">
-        <v>1</v>
-      </c>
-      <c r="F37" s="1"/>
-      <c r="H37" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>221</v>
-      </c>
-      <c r="B38" t="s">
-        <v>243</v>
-      </c>
-      <c r="C38" t="s">
-        <v>235</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E38">
-        <v>1</v>
-      </c>
-      <c r="F38" s="1"/>
-      <c r="G38" t="s">
-        <v>50</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>221</v>
-      </c>
-      <c r="B39" t="s">
-        <v>236</v>
-      </c>
-      <c r="C39" t="s">
-        <v>234</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E39">
-        <v>1</v>
-      </c>
-      <c r="F39" s="1"/>
-      <c r="H39" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>221</v>
-      </c>
-      <c r="B40" t="s">
-        <v>237</v>
-      </c>
-      <c r="C40" t="s">
-        <v>238</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E40">
-        <v>1</v>
-      </c>
-      <c r="F40" s="1"/>
-      <c r="H40" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>221</v>
-      </c>
-      <c r="B41" t="s">
-        <v>239</v>
-      </c>
-      <c r="C41" t="s">
-        <v>241</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E41">
-        <v>1</v>
-      </c>
-      <c r="F41" s="1"/>
-      <c r="G41" t="s">
-        <v>50</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>221</v>
-      </c>
-      <c r="B42" t="s">
-        <v>240</v>
-      </c>
-      <c r="C42" t="s">
-        <v>242</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E42">
-        <v>1</v>
-      </c>
-      <c r="F42" s="1"/>
-      <c r="G42" t="s">
-        <v>50</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>117</v>
-      </c>
-      <c r="B43" t="s">
-        <v>134</v>
-      </c>
-      <c r="C43" t="s">
-        <v>118</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E43">
-        <v>1</v>
-      </c>
-      <c r="G43" t="s">
-        <v>119</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>117</v>
-      </c>
-      <c r="B44" t="s">
-        <v>135</v>
-      </c>
-      <c r="C44" t="s">
-        <v>125</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E44">
-        <v>1</v>
-      </c>
-      <c r="G44" t="s">
-        <v>126</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>117</v>
-      </c>
-      <c r="B45" t="s">
-        <v>265</v>
-      </c>
-      <c r="C45" t="s">
-        <v>266</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E45">
-        <v>1</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>132</v>
-      </c>
-      <c r="B46" t="s">
-        <v>140</v>
-      </c>
-      <c r="C46" t="s">
-        <v>133</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E46">
-        <v>1</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>132</v>
-      </c>
-      <c r="B47" t="s">
-        <v>136</v>
-      </c>
-      <c r="C47" t="s">
-        <v>137</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E47">
-        <v>1</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>132</v>
-      </c>
-      <c r="B48" t="s">
-        <v>141</v>
-      </c>
-      <c r="C48" t="s">
-        <v>138</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E48">
-        <v>1</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>132</v>
-      </c>
-      <c r="B49" t="s">
-        <v>142</v>
-      </c>
-      <c r="C49" t="s">
-        <v>139</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E49">
-        <v>1</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>145</v>
-      </c>
-      <c r="B50" t="s">
-        <v>146</v>
-      </c>
-      <c r="C50" t="s">
-        <v>148</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E50">
-        <v>1</v>
-      </c>
-      <c r="G50" t="s">
-        <v>50</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>145</v>
-      </c>
-      <c r="B51" t="s">
-        <v>147</v>
-      </c>
-      <c r="C51" t="s">
-        <v>149</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E51">
-        <v>1</v>
-      </c>
-      <c r="G51" t="s">
-        <v>50</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>145</v>
-      </c>
-      <c r="B52" t="s">
-        <v>159</v>
-      </c>
-      <c r="C52" t="s">
-        <v>150</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E52">
-        <v>1</v>
-      </c>
-      <c r="G52" t="s">
-        <v>153</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>145</v>
-      </c>
-      <c r="B53" t="s">
-        <v>151</v>
-      </c>
-      <c r="C53" t="s">
-        <v>152</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E53">
-        <v>1</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>211</v>
-      </c>
-      <c r="B54" t="s">
-        <v>212</v>
-      </c>
-      <c r="C54" t="s">
-        <v>213</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E54">
-        <v>1</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>211</v>
-      </c>
-      <c r="B55" t="s">
-        <v>214</v>
-      </c>
-      <c r="C55" t="s">
-        <v>215</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E55">
-        <v>1</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>196</v>
-      </c>
-      <c r="B56" t="s">
-        <v>198</v>
-      </c>
-      <c r="C56" t="s">
-        <v>199</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E56">
-        <v>1</v>
-      </c>
-      <c r="G56" t="s">
-        <v>113</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>196</v>
-      </c>
-      <c r="B57" t="s">
-        <v>197</v>
-      </c>
-      <c r="C57" t="s">
-        <v>208</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E57">
-        <v>1</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>196</v>
-      </c>
-      <c r="B58" t="s">
-        <v>200</v>
-      </c>
-      <c r="C58" t="s">
-        <v>179</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E58">
-        <v>1</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>204</v>
-      </c>
-      <c r="B59" t="s">
-        <v>206</v>
-      </c>
-      <c r="C59" t="s">
-        <v>199</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E59">
-        <v>1</v>
-      </c>
-      <c r="G59" t="s">
-        <v>113</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>204</v>
-      </c>
-      <c r="B60" t="s">
-        <v>205</v>
-      </c>
-      <c r="C60" t="s">
-        <v>208</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E60">
-        <v>1</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>204</v>
-      </c>
-      <c r="B61" t="s">
-        <v>207</v>
-      </c>
-      <c r="C61" t="s">
-        <v>179</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E61">
-        <v>1</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>273</v>
-      </c>
-      <c r="B62" t="s">
-        <v>109</v>
-      </c>
-      <c r="C62" t="s">
-        <v>114</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E62">
-        <v>1</v>
-      </c>
-      <c r="G62" t="s">
-        <v>113</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>273</v>
-      </c>
-      <c r="B63" t="s">
-        <v>274</v>
-      </c>
-      <c r="C63" t="s">
-        <v>275</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E63">
-        <v>1</v>
-      </c>
-      <c r="G63" t="s">
-        <v>276</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>273</v>
-      </c>
-      <c r="B64" t="s">
-        <v>280</v>
-      </c>
-      <c r="C64" t="s">
-        <v>179</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E64">
-        <v>1</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>183</v>
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -3368,7 +3529,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{256469AD-8C25-494B-B7FC-7D7B2DDE1DC0}">
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -3378,10 +3539,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -3389,684 +3550,783 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B4">
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B5">
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B6">
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>321</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B14" t="s">
-        <v>251</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>252</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B15" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C15" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B17" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C17" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B18" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C19" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C20" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
+        <v>75</v>
+      </c>
+      <c r="B21" t="s">
+        <v>252</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>257</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>220</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>322</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>51</v>
+        <v>214</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33" t="s">
         <v>91</v>
-      </c>
-      <c r="B33">
-        <v>4</v>
-      </c>
-      <c r="C33" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B34">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B35">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C37" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C40" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C41" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C44" t="s">
-        <v>155</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C45" t="s">
-        <v>156</v>
+        <v>98</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C48" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C49" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C52" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C53" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>39</v>
+        <v>182</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>225</v>
+        <v>181</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>227</v>
+        <v>183</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>225</v>
+        <v>181</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>228</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>246</v>
+        <v>219</v>
       </c>
       <c r="B57">
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>249</v>
+        <v>221</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>246</v>
+        <v>219</v>
       </c>
       <c r="B58">
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>37</v>
+        <v>222</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>36</v>
+        <v>243</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B60">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="B61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C61" t="s">
-        <v>278</v>
+        <v>32</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C62" t="s">
-        <v>279</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="C63" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>271</v>
+      </c>
+      <c r="B64">
+        <v>2</v>
+      </c>
+      <c r="C64" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>271</v>
+      </c>
+      <c r="B65">
         <v>3</v>
       </c>
-      <c r="C63" t="s">
-        <v>296</v>
+      <c r="C65" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>304</v>
+      </c>
+      <c r="B66">
+        <v>1</v>
+      </c>
+      <c r="C66" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>304</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
+      </c>
+      <c r="C67" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>304</v>
+      </c>
+      <c r="B68">
+        <v>3</v>
+      </c>
+      <c r="C68" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>304</v>
+      </c>
+      <c r="B69">
+        <v>4</v>
+      </c>
+      <c r="C69" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>304</v>
+      </c>
+      <c r="B70">
+        <v>5</v>
+      </c>
+      <c r="C70" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>304</v>
+      </c>
+      <c r="B71">
+        <v>6</v>
+      </c>
+      <c r="C71" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>304</v>
+      </c>
+      <c r="B72">
+        <v>7</v>
+      </c>
+      <c r="C72" t="s">
+        <v>311</v>
       </c>
     </row>
   </sheetData>
